--- a/config/Ajio_dropdown.xlsx
+++ b/config/Ajio_dropdown.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\our data\KPA\Myntra\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDC67840-A516-47B0-9EAF-AB874C2F4579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD21E186-447A-45C2-AAAA-59AC2983C70B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="748" xr2:uid="{C0D2C78A-6BFE-401C-9027-E5C9268B4C7B}"/>
   </bookViews>

--- a/config/Ajio_dropdown.xlsx
+++ b/config/Ajio_dropdown.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\our data\KPA\Myntra\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD21E186-447A-45C2-AAAA-59AC2983C70B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F13A344C-23D0-4676-A32E-45CFEFCCED8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="748" xr2:uid="{C0D2C78A-6BFE-401C-9027-E5C9268B4C7B}"/>
   </bookViews>

--- a/config/Ajio_dropdown.xlsx
+++ b/config/Ajio_dropdown.xlsx
@@ -5,26 +5,29 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\our data\KPA\Myntra\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\our data\KPA\NEW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F13A344C-23D0-4676-A32E-45CFEFCCED8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABD5CBBD-F022-4C9F-98C7-F84F815C62EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="748" xr2:uid="{C0D2C78A-6BFE-401C-9027-E5C9268B4C7B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="748" activeTab="1" xr2:uid="{C0D2C78A-6BFE-401C-9027-E5C9268B4C7B}"/>
   </bookViews>
   <sheets>
-    <sheet name="ActualColorDropdown-Tshirts" sheetId="5" r:id="rId1"/>
+    <sheet name="Dropdown-Tshirts" sheetId="5" r:id="rId1"/>
+    <sheet name="Dropdown-Kids Tshirts" sheetId="6" r:id="rId2"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId2"/>
+    <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ActualColorDropdown-Tshirts'!$A$1:$D$1</definedName>
-    <definedName name="hid1den">[1]sheetForStoringExtraValues!$B$1:$B$6</definedName>
-    <definedName name="hid29den">[1]sheetForStoringExtraValues!$AD$1:$AD$6</definedName>
-    <definedName name="hid2den">[1]sheetForStoringExtraValues!$C$1:$C$2</definedName>
-    <definedName name="hid3den">[1]sheetForStoringExtraValues!$D$1:$D$5</definedName>
-    <definedName name="hid4den">[1]sheetForStoringExtraValues!$E$1:$E$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dropdown-Kids Tshirts'!$A$1:$D$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dropdown-Tshirts'!$A$1:$D$1</definedName>
+    <definedName name="hid1den">#REF!</definedName>
+    <definedName name="hid23den">[1]sheetForStoringExtraValues!$X$1:$X$234</definedName>
+    <definedName name="hid29den">#REF!</definedName>
+    <definedName name="hid2den">#REF!</definedName>
+    <definedName name="hid3den">#REF!</definedName>
+    <definedName name="hid4den">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="96">
   <si>
     <t>Blue</t>
   </si>
@@ -109,9 +112,6 @@
     <t>Round Neck</t>
   </si>
   <si>
-    <t>Final Category</t>
-  </si>
-  <si>
     <t>Closure</t>
   </si>
   <si>
@@ -275,6 +275,69 @@
   </si>
   <si>
     <t>Feature</t>
+  </si>
+  <si>
+    <t>Cars</t>
+  </si>
+  <si>
+    <t>Avengers</t>
+  </si>
+  <si>
+    <t>The Avengers</t>
+  </si>
+  <si>
+    <t>Spider-Man</t>
+  </si>
+  <si>
+    <t>Toy Story</t>
+  </si>
+  <si>
+    <t>Winnie The Pooh</t>
+  </si>
+  <si>
+    <t>Winnie-the-Pooh</t>
+  </si>
+  <si>
+    <t>Black</t>
+  </si>
+  <si>
+    <t>Red</t>
+  </si>
+  <si>
+    <t>60% Cotton 40% Polyester</t>
+  </si>
+  <si>
+    <t>2-3Y</t>
+  </si>
+  <si>
+    <t>3-4Y</t>
+  </si>
+  <si>
+    <t>4-5Y</t>
+  </si>
+  <si>
+    <t>5-6Y</t>
+  </si>
+  <si>
+    <t>6-7Y</t>
+  </si>
+  <si>
+    <t>7-8Y</t>
+  </si>
+  <si>
+    <t>8-9Y</t>
+  </si>
+  <si>
+    <t>10-11Y</t>
+  </si>
+  <si>
+    <t>11-12Y</t>
+  </si>
+  <si>
+    <t>13-14Y</t>
+  </si>
+  <si>
+    <t>Ajio Category</t>
   </si>
 </sst>
 </file>
@@ -344,7 +407,28 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -367,7 +451,7 @@
       <sheetName val="Template Instructions"/>
       <sheetName val="Image Guidelines"/>
       <sheetName val="sheetForStoringExtraValues"/>
-      <sheetName val="830316018_Styles_Tshirts"/>
+      <sheetName val="830501001_Styles_Tshirts"/>
       <sheetName val="Seller Information Sheet"/>
     </sheetNames>
     <sheetDataSet>
@@ -375,90 +459,1173 @@
       <sheetData sheetId="1"/>
       <sheetData sheetId="2">
         <row r="1">
-          <cell r="B1" t="str">
-            <v>Casual</v>
-          </cell>
-          <cell r="C1" t="str">
-            <v>Fashion</v>
-          </cell>
-          <cell r="D1" t="str">
-            <v>Summer</v>
-          </cell>
-          <cell r="E1" t="str">
-            <v>2021</v>
-          </cell>
-          <cell r="AD1" t="str">
-            <v>Single</v>
+          <cell r="X1" t="str">
+            <v>Aladdin</v>
           </cell>
         </row>
         <row r="2">
-          <cell r="B2" t="str">
-            <v>Evening</v>
-          </cell>
-          <cell r="C2" t="str">
-            <v>Core</v>
-          </cell>
-          <cell r="D2" t="str">
-            <v>Spring</v>
-          </cell>
-          <cell r="E2" t="str">
-            <v>2022</v>
-          </cell>
-          <cell r="AD2" t="str">
-            <v>Pack of 2</v>
+          <cell r="X2" t="str">
+            <v>Angry Birds</v>
           </cell>
         </row>
         <row r="3">
-          <cell r="B3" t="str">
-            <v>Occasion</v>
-          </cell>
-          <cell r="D3" t="str">
-            <v>Winter</v>
-          </cell>
-          <cell r="E3" t="str">
-            <v>2023</v>
-          </cell>
-          <cell r="AD3" t="str">
-            <v>Pack of 3</v>
+          <cell r="X3" t="str">
+            <v>Barbie</v>
           </cell>
         </row>
         <row r="4">
-          <cell r="B4" t="str">
-            <v>Work</v>
-          </cell>
-          <cell r="D4" t="str">
-            <v>Fall</v>
-          </cell>
-          <cell r="E4" t="str">
-            <v>2024</v>
-          </cell>
-          <cell r="AD4" t="str">
-            <v>Pack of 4</v>
+          <cell r="X4" t="str">
+            <v>Ben 10</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="B5" t="str">
-            <v>Active</v>
-          </cell>
-          <cell r="D5" t="str">
-            <v>Core</v>
-          </cell>
-          <cell r="E5" t="str">
-            <v>2025</v>
-          </cell>
-          <cell r="AD5" t="str">
-            <v>Pack of 5</v>
+          <cell r="X5" t="str">
+            <v>Bob the Builder</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="B6" t="str">
-            <v>Universal</v>
-          </cell>
-          <cell r="E6" t="str">
-            <v>2026</v>
-          </cell>
-          <cell r="AD6" t="str">
-            <v>Multi Pack</v>
+          <cell r="X6" t="str">
+            <v>Bugs Bunny</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="X7" t="str">
+            <v>Captain America</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="X8" t="str">
+            <v>Chhota Bheem</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="X9" t="str">
+            <v>Chutki</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="X10" t="str">
+            <v>Cinderella</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="X11" t="str">
+            <v>DC Comics</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="X12" t="str">
+            <v>Deadpool</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="X13" t="str">
+            <v>Doctor Strange</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="X14" t="str">
+            <v>Donald Duck</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="X15" t="str">
+            <v>Dora</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="X16" t="str">
+            <v>Doremon</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="X17" t="str">
+            <v>DuckTales</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="X18" t="str">
+            <v>Frozen</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="X19" t="str">
+            <v>Genie</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="X20" t="str">
+            <v>Goku</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="X21" t="str">
+            <v>Goofy</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="X22" t="str">
+            <v>Groot</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="X23" t="str">
+            <v>Harry Potter</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="X24" t="str">
+            <v>Hello Kitty</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="X25" t="str">
+            <v>Hercules</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="X26" t="str">
+            <v>Hulk</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="X27" t="str">
+            <v>Iron Man</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="X28" t="str">
+            <v>Joker</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="X29" t="str">
+            <v>Jurassic World</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="X30" t="str">
+            <v>Kung Fu Panda</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="X31" t="str">
+            <v>Marvel</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="X32" t="str">
+            <v>Mickey Mouse</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="X33" t="str">
+            <v>Minions</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="X34" t="str">
+            <v>Motu Patlu</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="X35" t="str">
+            <v>Noddy</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="X36" t="str">
+            <v>Oggy and the Cockroaches</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="X37" t="str">
+            <v>Peter Pan</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="X38" t="str">
+            <v>Pluto</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="X39" t="str">
+            <v>Pokemon</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="X40" t="str">
+            <v>Popeye</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="X41" t="str">
+            <v>Scooby-Doo</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="X42" t="str">
+            <v>Shin-Chan</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="X43" t="str">
+            <v>Spider-Man</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="X44" t="str">
+            <v>SpongeBob SquarePants</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="X45" t="str">
+            <v>Star Trek</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="X46" t="str">
+            <v>Star Wars</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="X47" t="str">
+            <v>Superman</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="X48" t="str">
+            <v>Teenage Mutant Ninja Turtles</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="X49" t="str">
+            <v>The Avengers</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="X50" t="str">
+            <v>The Flash</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="X51" t="str">
+            <v>The Flintstones</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="X52" t="str">
+            <v>The Incredibles</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="X53" t="str">
+            <v>The Jungle Book</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="X54" t="str">
+            <v>The Little Mermaid</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="X55" t="str">
+            <v>The Powerpuff Girls</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="X56" t="str">
+            <v>Tinker Bell</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="X57" t="str">
+            <v>Tom and Jerry</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="X58" t="str">
+            <v>Transformers</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="X59" t="str">
+            <v>Winnie-the-Pooh</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="X60" t="str">
+            <v>Wolverine</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="X61" t="str">
+            <v>Wonder Woman</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="X62" t="str">
+            <v>WWE</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="X63" t="str">
+            <v>X-Men</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="X64" t="str">
+            <v>101 Dalmatians</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="X65" t="str">
+            <v>AC Milan</v>
+          </cell>
+        </row>
+        <row r="66">
+          <cell r="X66" t="str">
+            <v>AC/DC</v>
+          </cell>
+        </row>
+        <row r="67">
+          <cell r="X67" t="str">
+            <v>Annabelle</v>
+          </cell>
+        </row>
+        <row r="68">
+          <cell r="X68" t="str">
+            <v>Ant-Man</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="X69" t="str">
+            <v>Aquaman</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="X70" t="str">
+            <v>Archie</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="X71" t="str">
+            <v>Arrow</v>
+          </cell>
+        </row>
+        <row r="72">
+          <cell r="X72" t="str">
+            <v>Arsenal</v>
+          </cell>
+        </row>
+        <row r="73">
+          <cell r="X73" t="str">
+            <v>Attack on Titan</v>
+          </cell>
+        </row>
+        <row r="74">
+          <cell r="X74" t="str">
+            <v>Avatar</v>
+          </cell>
+        </row>
+        <row r="75">
+          <cell r="X75" t="str">
+            <v>Backstreet Boys</v>
+          </cell>
+        </row>
+        <row r="76">
+          <cell r="X76" t="str">
+            <v>Batman</v>
+          </cell>
+        </row>
+        <row r="77">
+          <cell r="X77" t="str">
+            <v>Bayern Munich</v>
+          </cell>
+        </row>
+        <row r="78">
+          <cell r="X78" t="str">
+            <v>Beach Boys</v>
+          </cell>
+        </row>
+        <row r="79">
+          <cell r="X79" t="str">
+            <v>Billie Eilish</v>
+          </cell>
+        </row>
+        <row r="80">
+          <cell r="X80" t="str">
+            <v>Blackpink</v>
+          </cell>
+        </row>
+        <row r="81">
+          <cell r="X81" t="str">
+            <v>BMW Motorsport</v>
+          </cell>
+        </row>
+        <row r="82">
+          <cell r="X82" t="str">
+            <v>Boston Celtics</v>
+          </cell>
+        </row>
+        <row r="83">
+          <cell r="X83" t="str">
+            <v>Breaking Bad</v>
+          </cell>
+        </row>
+        <row r="84">
+          <cell r="X84" t="str">
+            <v>Brooklyn Nets</v>
+          </cell>
+        </row>
+        <row r="85">
+          <cell r="X85" t="str">
+            <v>BTS</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="X86" t="str">
+            <v>Bubble Guppies</v>
+          </cell>
+        </row>
+        <row r="87">
+          <cell r="X87" t="str">
+            <v>Call of Duty</v>
+          </cell>
+        </row>
+        <row r="88">
+          <cell r="X88" t="str">
+            <v>Calvin &amp; Hobbes</v>
+          </cell>
+        </row>
+        <row r="89">
+          <cell r="X89" t="str">
+            <v>Cartoon Network</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="X90" t="str">
+            <v>Catwoman</v>
+          </cell>
+        </row>
+        <row r="91">
+          <cell r="X91" t="str">
+            <v>Che Guevara</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="X92" t="str">
+            <v>Chelsea</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="X93" t="str">
+            <v>Chennai Super Kings</v>
+          </cell>
+        </row>
+        <row r="94">
+          <cell r="X94" t="str">
+            <v>Chicago Bulls</v>
+          </cell>
+        </row>
+        <row r="95">
+          <cell r="X95" t="str">
+            <v>Clifford</v>
+          </cell>
+        </row>
+        <row r="96">
+          <cell r="X96" t="str">
+            <v>Coldplay</v>
+          </cell>
+        </row>
+        <row r="97">
+          <cell r="X97" t="str">
+            <v>Courage the Cowardly Dog</v>
+          </cell>
+        </row>
+        <row r="98">
+          <cell r="X98" t="str">
+            <v>Dallas Mavericks</v>
+          </cell>
+        </row>
+        <row r="99">
+          <cell r="X99" t="str">
+            <v>Daredevil</v>
+          </cell>
+        </row>
+        <row r="100">
+          <cell r="X100" t="str">
+            <v>Darth Vader</v>
+          </cell>
+        </row>
+        <row r="101">
+          <cell r="X101" t="str">
+            <v>DC Movie Universe</v>
+          </cell>
+        </row>
+        <row r="102">
+          <cell r="X102" t="str">
+            <v>Delhi Capitals</v>
+          </cell>
+        </row>
+        <row r="103">
+          <cell r="X103" t="str">
+            <v>Demon Slayer</v>
+          </cell>
+        </row>
+        <row r="104">
+          <cell r="X104" t="str">
+            <v>Dexter</v>
+          </cell>
+        </row>
+        <row r="105">
+          <cell r="X105" t="str">
+            <v>Diego</v>
+          </cell>
+        </row>
+        <row r="106">
+          <cell r="X106" t="str">
+            <v>Disney</v>
+          </cell>
+        </row>
+        <row r="107">
+          <cell r="X107" t="str">
+            <v>Dragon Ball Z</v>
+          </cell>
+        </row>
+        <row r="108">
+          <cell r="X108" t="str">
+            <v>Dragon Booster</v>
+          </cell>
+        </row>
+        <row r="109">
+          <cell r="X109" t="str">
+            <v>Eeyore</v>
+          </cell>
+        </row>
+        <row r="110">
+          <cell r="X110" t="str">
+            <v>Elvis Presley</v>
+          </cell>
+        </row>
+        <row r="111">
+          <cell r="X111" t="str">
+            <v>Eminem</v>
+          </cell>
+        </row>
+        <row r="112">
+          <cell r="X112" t="str">
+            <v>Eren</v>
+          </cell>
+        </row>
+        <row r="113">
+          <cell r="X113" t="str">
+            <v>Esports Teams</v>
+          </cell>
+        </row>
+        <row r="114">
+          <cell r="X114" t="str">
+            <v>Eternals</v>
+          </cell>
+        </row>
+        <row r="115">
+          <cell r="X115" t="str">
+            <v>Fantastic Beasts</v>
+          </cell>
+        </row>
+        <row r="116">
+          <cell r="X116" t="str">
+            <v>FC Barcelona</v>
+          </cell>
+        </row>
+        <row r="117">
+          <cell r="X117" t="str">
+            <v>Ferrari</v>
+          </cell>
+        </row>
+        <row r="118">
+          <cell r="X118" t="str">
+            <v>Fireman Sam</v>
+          </cell>
+        </row>
+        <row r="119">
+          <cell r="X119" t="str">
+            <v>Football Club Goa</v>
+          </cell>
+        </row>
+        <row r="120">
+          <cell r="X120" t="str">
+            <v>Formula 1</v>
+          </cell>
+        </row>
+        <row r="121">
+          <cell r="X121" t="str">
+            <v>Fortnite</v>
+          </cell>
+        </row>
+        <row r="122">
+          <cell r="X122" t="str">
+            <v>Free Fire</v>
+          </cell>
+        </row>
+        <row r="123">
+          <cell r="X123" t="str">
+            <v>G.I. Joe</v>
+          </cell>
+        </row>
+        <row r="124">
+          <cell r="X124" t="str">
+            <v>Ghost Rider</v>
+          </cell>
+        </row>
+        <row r="125">
+          <cell r="X125" t="str">
+            <v>Ghost Spider</v>
+          </cell>
+        </row>
+        <row r="126">
+          <cell r="X126" t="str">
+            <v>Godzilla</v>
+          </cell>
+        </row>
+        <row r="127">
+          <cell r="X127" t="str">
+            <v>Gojo</v>
+          </cell>
+        </row>
+        <row r="128">
+          <cell r="X128" t="str">
+            <v>Golden State Warriors</v>
+          </cell>
+        </row>
+        <row r="129">
+          <cell r="X129" t="str">
+            <v>Guardians of the Galaxy</v>
+          </cell>
+        </row>
+        <row r="130">
+          <cell r="X130" t="str">
+            <v>Gujarat Titans</v>
+          </cell>
+        </row>
+        <row r="131">
+          <cell r="X131" t="str">
+            <v>Guns N Roses</v>
+          </cell>
+        </row>
+        <row r="132">
+          <cell r="X132" t="str">
+            <v>Hannah Montana</v>
+          </cell>
+        </row>
+        <row r="133">
+          <cell r="X133" t="str">
+            <v>Hawkeye</v>
+          </cell>
+        </row>
+        <row r="134">
+          <cell r="X134" t="str">
+            <v>Hip Hop Icons</v>
+          </cell>
+        </row>
+        <row r="135">
+          <cell r="X135" t="str">
+            <v>Human Torch</v>
+          </cell>
+        </row>
+        <row r="136">
+          <cell r="X136" t="str">
+            <v>Indian Cricket Team</v>
+          </cell>
+        </row>
+        <row r="137">
+          <cell r="X137" t="str">
+            <v>Indiana Pacers</v>
+          </cell>
+        </row>
+        <row r="138">
+          <cell r="X138" t="str">
+            <v>Invisible Woman</v>
+          </cell>
+        </row>
+        <row r="139">
+          <cell r="X139" t="str">
+            <v>ISRO</v>
+          </cell>
+        </row>
+        <row r="140">
+          <cell r="X140" t="str">
+            <v>Itachi</v>
+          </cell>
+        </row>
+        <row r="141">
+          <cell r="X141" t="str">
+            <v>Johnny Bravo</v>
+          </cell>
+        </row>
+        <row r="142">
+          <cell r="X142" t="str">
+            <v>Jujutsu Kaisen</v>
+          </cell>
+        </row>
+        <row r="143">
+          <cell r="X143" t="str">
+            <v>Jurassic Park</v>
+          </cell>
+        </row>
+        <row r="144">
+          <cell r="X144" t="str">
+            <v>Juventus</v>
+          </cell>
+        </row>
+        <row r="145">
+          <cell r="X145" t="str">
+            <v>Ken</v>
+          </cell>
+        </row>
+        <row r="146">
+          <cell r="X146" t="str">
+            <v>Kolkata Knight Riders</v>
+          </cell>
+        </row>
+        <row r="147">
+          <cell r="X147" t="str">
+            <v>Kurt Cobain</v>
+          </cell>
+        </row>
+        <row r="148">
+          <cell r="X148" t="str">
+            <v>Levi</v>
+          </cell>
+        </row>
+        <row r="149">
+          <cell r="X149" t="str">
+            <v>Lilo &amp; Stitch</v>
+          </cell>
+        </row>
+        <row r="150">
+          <cell r="X150" t="str">
+            <v>Little Krishna</v>
+          </cell>
+        </row>
+        <row r="151">
+          <cell r="X151" t="str">
+            <v>Lord of the Rings</v>
+          </cell>
+        </row>
+        <row r="152">
+          <cell r="X152" t="str">
+            <v>Los Angeles Lakers</v>
+          </cell>
+        </row>
+        <row r="153">
+          <cell r="X153" t="str">
+            <v>Luffy</v>
+          </cell>
+        </row>
+        <row r="154">
+          <cell r="X154" t="str">
+            <v>Madagascar</v>
+          </cell>
+        </row>
+        <row r="155">
+          <cell r="X155" t="str">
+            <v>Manchester City</v>
+          </cell>
+        </row>
+        <row r="156">
+          <cell r="X156" t="str">
+            <v>Manchester United</v>
+          </cell>
+        </row>
+        <row r="157">
+          <cell r="X157" t="str">
+            <v>Max &amp; Ruby</v>
+          </cell>
+        </row>
+        <row r="158">
+          <cell r="X158" t="str">
+            <v>Mercedes-AMG Petronas</v>
+          </cell>
+        </row>
+        <row r="159">
+          <cell r="X159" t="str">
+            <v>Miami Heat</v>
+          </cell>
+        </row>
+        <row r="160">
+          <cell r="X160" t="str">
+            <v>Michael Jordan</v>
+          </cell>
+        </row>
+        <row r="161">
+          <cell r="X161" t="str">
+            <v>Minnie Mouse</v>
+          </cell>
+        </row>
+        <row r="162">
+          <cell r="X162" t="str">
+            <v>Mister Fantastic</v>
+          </cell>
+        </row>
+        <row r="163">
+          <cell r="X163" t="str">
+            <v>Money Heist</v>
+          </cell>
+        </row>
+        <row r="164">
+          <cell r="X164" t="str">
+            <v>Monsters Inc.</v>
+          </cell>
+        </row>
+        <row r="165">
+          <cell r="X165" t="str">
+            <v>Mortal Kombat</v>
+          </cell>
+        </row>
+        <row r="166">
+          <cell r="X166" t="str">
+            <v>MotoGP</v>
+          </cell>
+        </row>
+        <row r="167">
+          <cell r="X167" t="str">
+            <v>Mr Bean</v>
+          </cell>
+        </row>
+        <row r="168">
+          <cell r="X168" t="str">
+            <v>Mumbai Indians</v>
+          </cell>
+        </row>
+        <row r="169">
+          <cell r="X169" t="str">
+            <v>My Little Pony</v>
+          </cell>
+        </row>
+        <row r="170">
+          <cell r="X170" t="str">
+            <v>Naruto</v>
+          </cell>
+        </row>
+        <row r="171">
+          <cell r="X171" t="str">
+            <v>NASA</v>
+          </cell>
+        </row>
+        <row r="172">
+          <cell r="X172" t="str">
+            <v>NBA</v>
+          </cell>
+        </row>
+        <row r="173">
+          <cell r="X173" t="str">
+            <v>Nemo</v>
+          </cell>
+        </row>
+        <row r="174">
+          <cell r="X174" t="str">
+            <v>New Orleans Pelicans</v>
+          </cell>
+        </row>
+        <row r="175">
+          <cell r="X175" t="str">
+            <v>New York Knicks</v>
+          </cell>
+        </row>
+        <row r="176">
+          <cell r="X176" t="str">
+            <v>Nezuko</v>
+          </cell>
+        </row>
+        <row r="177">
+          <cell r="X177" t="str">
+            <v>Ninja Hattori</v>
+          </cell>
+        </row>
+        <row r="178">
+          <cell r="X178" t="str">
+            <v>Nirvana</v>
+          </cell>
+        </row>
+        <row r="179">
+          <cell r="X179" t="str">
+            <v>One Piece</v>
+          </cell>
+        </row>
+        <row r="180">
+          <cell r="X180" t="str">
+            <v>Others</v>
+          </cell>
+        </row>
+        <row r="181">
+          <cell r="X181" t="str">
+            <v>Outlander</v>
+          </cell>
+        </row>
+        <row r="182">
+          <cell r="X182" t="str">
+            <v>Paris Saint-Germain</v>
+          </cell>
+        </row>
+        <row r="183">
+          <cell r="X183" t="str">
+            <v>PAW Patrol</v>
+          </cell>
+        </row>
+        <row r="184">
+          <cell r="X184" t="str">
+            <v>Peanuts</v>
+          </cell>
+        </row>
+        <row r="185">
+          <cell r="X185" t="str">
+            <v>Phineas and Ferb</v>
+          </cell>
+        </row>
+        <row r="186">
+          <cell r="X186" t="str">
+            <v>Pink Floyd</v>
+          </cell>
+        </row>
+        <row r="187">
+          <cell r="X187" t="str">
+            <v>Pixar</v>
+          </cell>
+        </row>
+        <row r="188">
+          <cell r="X188" t="str">
+            <v>Porsche</v>
+          </cell>
+        </row>
+        <row r="189">
+          <cell r="X189" t="str">
+            <v>Power Rangers</v>
+          </cell>
+        </row>
+        <row r="190">
+          <cell r="X190" t="str">
+            <v>PUBG</v>
+          </cell>
+        </row>
+        <row r="191">
+          <cell r="X191" t="str">
+            <v>Punisher</v>
+          </cell>
+        </row>
+        <row r="192">
+          <cell r="X192" t="str">
+            <v>Punjab Kings</v>
+          </cell>
+        </row>
+        <row r="193">
+          <cell r="X193" t="str">
+            <v>Real Madrid</v>
+          </cell>
+        </row>
+        <row r="194">
+          <cell r="X194" t="str">
+            <v>Red Bull Racing</v>
+          </cell>
+        </row>
+        <row r="195">
+          <cell r="X195" t="str">
+            <v>Royal Challengers</v>
+          </cell>
+        </row>
+        <row r="196">
+          <cell r="X196" t="str">
+            <v>Sasuke</v>
+          </cell>
+        </row>
+        <row r="197">
+          <cell r="X197" t="str">
+            <v>Sesame Street</v>
+          </cell>
+        </row>
+        <row r="198">
+          <cell r="X198" t="str">
+            <v>Shaun the Sheep</v>
+          </cell>
+        </row>
+        <row r="199">
+          <cell r="X199" t="str">
+            <v>Sheriff Callie's Wild West</v>
+          </cell>
+        </row>
+        <row r="200">
+          <cell r="X200" t="str">
+            <v>Sherlock</v>
+          </cell>
+        </row>
+        <row r="201">
+          <cell r="X201" t="str">
+            <v>Shiva</v>
+          </cell>
+        </row>
+        <row r="202">
+          <cell r="X202" t="str">
+            <v>Silver Surfer</v>
+          </cell>
+        </row>
+        <row r="203">
+          <cell r="X203" t="str">
+            <v>Simba</v>
+          </cell>
+        </row>
+        <row r="204">
+          <cell r="X204" t="str">
+            <v>Snoopy</v>
+          </cell>
+        </row>
+        <row r="205">
+          <cell r="X205" t="str">
+            <v>Sofia the First</v>
+          </cell>
+        </row>
+        <row r="206">
+          <cell r="X206" t="str">
+            <v>Squid Game</v>
+          </cell>
+        </row>
+        <row r="207">
+          <cell r="X207" t="str">
+            <v>Storm</v>
+          </cell>
+        </row>
+        <row r="208">
+          <cell r="X208" t="str">
+            <v>Street Fighter</v>
+          </cell>
+        </row>
+        <row r="209">
+          <cell r="X209" t="str">
+            <v>Sukuna</v>
+          </cell>
+        </row>
+        <row r="210">
+          <cell r="X210" t="str">
+            <v>Sunrisers Hyderabad</v>
+          </cell>
+        </row>
+        <row r="211">
+          <cell r="X211" t="str">
+            <v>Super Mario</v>
+          </cell>
+        </row>
+        <row r="212">
+          <cell r="X212" t="str">
+            <v>Super Spy</v>
+          </cell>
+        </row>
+        <row r="213">
+          <cell r="X213" t="str">
+            <v>SWAT Kats</v>
+          </cell>
+        </row>
+        <row r="214">
+          <cell r="X214" t="str">
+            <v>Sylvester</v>
+          </cell>
+        </row>
+        <row r="215">
+          <cell r="X215" t="str">
+            <v>Taylor Swift</v>
+          </cell>
+        </row>
+        <row r="216">
+          <cell r="X216" t="str">
+            <v>Team Umizoomi</v>
+          </cell>
+        </row>
+        <row r="217">
+          <cell r="X217" t="str">
+            <v>The Beatles</v>
+          </cell>
+        </row>
+        <row r="218">
+          <cell r="X218" t="str">
+            <v>The Boys</v>
+          </cell>
+        </row>
+        <row r="219">
+          <cell r="X219" t="str">
+            <v>The Pink Panther</v>
+          </cell>
+        </row>
+        <row r="220">
+          <cell r="X220" t="str">
+            <v>The Rolling Stones</v>
+          </cell>
+        </row>
+        <row r="221">
+          <cell r="X221" t="str">
+            <v>The Simpsons</v>
+          </cell>
+        </row>
+        <row r="222">
+          <cell r="X222" t="str">
+            <v>The Weeknd</v>
+          </cell>
+        </row>
+        <row r="223">
+          <cell r="X223" t="str">
+            <v>Thomas &amp; Friends</v>
+          </cell>
+        </row>
+        <row r="224">
+          <cell r="X224" t="str">
+            <v>Thor</v>
+          </cell>
+        </row>
+        <row r="225">
+          <cell r="X225" t="str">
+            <v>Tiger King</v>
+          </cell>
+        </row>
+        <row r="226">
+          <cell r="X226" t="str">
+            <v>Toy Story</v>
+          </cell>
+        </row>
+        <row r="227">
+          <cell r="X227" t="str">
+            <v>Travis Scott</v>
+          </cell>
+        </row>
+        <row r="228">
+          <cell r="X228" t="str">
+            <v>Tweetie Pie</v>
+          </cell>
+        </row>
+        <row r="229">
+          <cell r="X229" t="str">
+            <v>Vegeta</v>
+          </cell>
+        </row>
+        <row r="230">
+          <cell r="X230" t="str">
+            <v>Venom</v>
+          </cell>
+        </row>
+        <row r="231">
+          <cell r="X231" t="str">
+            <v>We Bare Bears</v>
+          </cell>
+        </row>
+        <row r="232">
+          <cell r="X232" t="str">
+            <v>Winx Club</v>
+          </cell>
+        </row>
+        <row r="233">
+          <cell r="X233" t="str">
+            <v>Zenitsu</v>
+          </cell>
+        </row>
+        <row r="234">
+          <cell r="X234" t="str">
+            <v>Zoro</v>
           </cell>
         </row>
       </sheetData>
@@ -805,149 +1972,149 @@
         <v>7</v>
       </c>
       <c r="D1" t="s">
-        <v>20</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" t="s">
         <v>40</v>
       </c>
-      <c r="B2" t="s">
-        <v>41</v>
-      </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C3" t="s">
         <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
         <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C5" t="s">
         <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
         <v>45</v>
       </c>
-      <c r="B6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" t="s">
-        <v>46</v>
-      </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" t="s">
         <v>47</v>
       </c>
-      <c r="B7" t="s">
-        <v>48</v>
-      </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
         <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B11">
         <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B12" t="s">
         <v>2</v>
@@ -956,12 +2123,12 @@
         <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B13" t="s">
         <v>0</v>
@@ -970,12 +2137,12 @@
         <v>0</v>
       </c>
       <c r="D13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B14" t="s">
         <v>1</v>
@@ -984,12 +2151,12 @@
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B15" t="s">
         <v>4</v>
@@ -998,12 +2165,12 @@
         <v>4</v>
       </c>
       <c r="D15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B16" t="s">
         <v>3</v>
@@ -1012,222 +2179,222 @@
         <v>0</v>
       </c>
       <c r="D16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C17" t="s">
         <v>17</v>
       </c>
       <c r="D17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" t="s">
         <v>55</v>
       </c>
-      <c r="B18" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" t="s">
-        <v>56</v>
-      </c>
       <c r="D18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" t="s">
         <v>55</v>
       </c>
-      <c r="B19" t="s">
-        <v>37</v>
-      </c>
-      <c r="C19" t="s">
-        <v>56</v>
-      </c>
       <c r="D19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" t="s">
         <v>57</v>
       </c>
-      <c r="B20" t="s">
-        <v>29</v>
-      </c>
-      <c r="C20" t="s">
-        <v>58</v>
-      </c>
       <c r="D20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
+        <v>59</v>
+      </c>
+      <c r="B22" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" t="s">
         <v>60</v>
       </c>
-      <c r="B22" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" t="s">
-        <v>61</v>
-      </c>
       <c r="D22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C25" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B27" t="s">
         <v>19</v>
       </c>
       <c r="C27" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D27" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B28">
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B29">
         <v>2</v>
       </c>
       <c r="C29" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D29" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B30" t="s">
         <v>18</v>
       </c>
       <c r="C30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31" t="s">
+        <v>28</v>
+      </c>
+      <c r="C31" t="s">
         <v>33</v>
       </c>
-      <c r="B31" t="s">
-        <v>29</v>
-      </c>
-      <c r="C31" t="s">
-        <v>34</v>
-      </c>
       <c r="D31" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B32" t="s">
         <v>13</v>
@@ -1236,12 +2403,12 @@
         <v>13</v>
       </c>
       <c r="D32" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B33" t="s">
         <v>8</v>
@@ -1250,12 +2417,12 @@
         <v>8</v>
       </c>
       <c r="D33" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B34" t="s">
         <v>9</v>
@@ -1264,12 +2431,12 @@
         <v>9</v>
       </c>
       <c r="D34" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B35" t="s">
         <v>10</v>
@@ -1278,12 +2445,12 @@
         <v>10</v>
       </c>
       <c r="D35" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B36" t="s">
         <v>11</v>
@@ -1292,26 +2459,26 @@
         <v>11</v>
       </c>
       <c r="D36" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B37" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C37" t="s">
         <v>12</v>
       </c>
       <c r="D37" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B38" t="s">
         <v>12</v>
@@ -1320,63 +2487,63 @@
         <v>12</v>
       </c>
       <c r="D38" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B39" t="s">
         <v>19</v>
       </c>
       <c r="C39" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D39" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B40" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C40" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D40" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
+        <v>72</v>
+      </c>
+      <c r="B41" t="s">
+        <v>28</v>
+      </c>
+      <c r="C41" t="s">
         <v>73</v>
       </c>
-      <c r="B41" t="s">
-        <v>29</v>
-      </c>
-      <c r="C41" t="s">
-        <v>74</v>
-      </c>
       <c r="D41" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B42" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C42" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D42" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1399,4 +2566,753 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5E74C28-9494-4104-81C6-5A34A8ECDBE0}">
+  <dimension ref="A1:D51"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="27.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="12.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" t="s">
+        <v>75</v>
+      </c>
+      <c r="D9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11" t="s">
+        <v>78</v>
+      </c>
+      <c r="D11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12" t="s">
+        <v>79</v>
+      </c>
+      <c r="D12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13" t="s">
+        <v>81</v>
+      </c>
+      <c r="D13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>51</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16">
+        <v>2</v>
+      </c>
+      <c r="C16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" t="s">
+        <v>0</v>
+      </c>
+      <c r="C18" t="s">
+        <v>0</v>
+      </c>
+      <c r="D18" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1</v>
+      </c>
+      <c r="D19" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D20" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" t="s">
+        <v>3</v>
+      </c>
+      <c r="C21" t="s">
+        <v>0</v>
+      </c>
+      <c r="D21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" t="s">
+        <v>82</v>
+      </c>
+      <c r="C22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D22" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>52</v>
+      </c>
+      <c r="B23" t="s">
+        <v>83</v>
+      </c>
+      <c r="C23" t="s">
+        <v>83</v>
+      </c>
+      <c r="D23" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>53</v>
+      </c>
+      <c r="B25" t="s">
+        <v>84</v>
+      </c>
+      <c r="C25" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>54</v>
+      </c>
+      <c r="B26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" t="s">
+        <v>55</v>
+      </c>
+      <c r="D26" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>56</v>
+      </c>
+      <c r="B28" t="s">
+        <v>28</v>
+      </c>
+      <c r="C28" t="s">
+        <v>57</v>
+      </c>
+      <c r="D28" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>59</v>
+      </c>
+      <c r="B29" t="s">
+        <v>37</v>
+      </c>
+      <c r="C29" t="s">
+        <v>60</v>
+      </c>
+      <c r="D29" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" t="s">
+        <v>27</v>
+      </c>
+      <c r="D30" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>62</v>
+      </c>
+      <c r="B31" t="s">
+        <v>28</v>
+      </c>
+      <c r="C31" t="s">
+        <v>30</v>
+      </c>
+      <c r="D31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32" t="s">
+        <v>21</v>
+      </c>
+      <c r="C32" t="s">
+        <v>38</v>
+      </c>
+      <c r="D32" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>63</v>
+      </c>
+      <c r="B33" t="s">
+        <v>24</v>
+      </c>
+      <c r="C33" t="s">
+        <v>24</v>
+      </c>
+      <c r="D33" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>64</v>
+      </c>
+      <c r="B34" t="s">
+        <v>19</v>
+      </c>
+      <c r="C34" t="s">
+        <v>65</v>
+      </c>
+      <c r="D34" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>66</v>
+      </c>
+      <c r="B35">
+        <v>1</v>
+      </c>
+      <c r="C35" t="s">
+        <v>29</v>
+      </c>
+      <c r="D35" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>66</v>
+      </c>
+      <c r="B36">
+        <v>2</v>
+      </c>
+      <c r="C36" t="s">
+        <v>67</v>
+      </c>
+      <c r="D36" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>32</v>
+      </c>
+      <c r="B37" t="s">
+        <v>28</v>
+      </c>
+      <c r="C37" t="s">
+        <v>33</v>
+      </c>
+      <c r="D37" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>69</v>
+      </c>
+      <c r="B38" t="s">
+        <v>85</v>
+      </c>
+      <c r="C38" t="s">
+        <v>85</v>
+      </c>
+      <c r="D38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>69</v>
+      </c>
+      <c r="B39" t="s">
+        <v>86</v>
+      </c>
+      <c r="C39" t="s">
+        <v>86</v>
+      </c>
+      <c r="D39" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>69</v>
+      </c>
+      <c r="B40" t="s">
+        <v>87</v>
+      </c>
+      <c r="C40" t="s">
+        <v>87</v>
+      </c>
+      <c r="D40" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>69</v>
+      </c>
+      <c r="B41" t="s">
+        <v>88</v>
+      </c>
+      <c r="C41" t="s">
+        <v>88</v>
+      </c>
+      <c r="D41" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>69</v>
+      </c>
+      <c r="B42" t="s">
+        <v>89</v>
+      </c>
+      <c r="C42" t="s">
+        <v>89</v>
+      </c>
+      <c r="D42" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>69</v>
+      </c>
+      <c r="B43" t="s">
+        <v>90</v>
+      </c>
+      <c r="C43" t="s">
+        <v>90</v>
+      </c>
+      <c r="D43" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>69</v>
+      </c>
+      <c r="B44" t="s">
+        <v>91</v>
+      </c>
+      <c r="C44" t="s">
+        <v>91</v>
+      </c>
+      <c r="D44" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>69</v>
+      </c>
+      <c r="B45" t="s">
+        <v>92</v>
+      </c>
+      <c r="C45" t="s">
+        <v>92</v>
+      </c>
+      <c r="D45" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>69</v>
+      </c>
+      <c r="B46" t="s">
+        <v>93</v>
+      </c>
+      <c r="C46" t="s">
+        <v>93</v>
+      </c>
+      <c r="D46" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>69</v>
+      </c>
+      <c r="B47" t="s">
+        <v>94</v>
+      </c>
+      <c r="C47" t="s">
+        <v>94</v>
+      </c>
+      <c r="D47" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>70</v>
+      </c>
+      <c r="B48" t="s">
+        <v>19</v>
+      </c>
+      <c r="C48" t="s">
+        <v>65</v>
+      </c>
+      <c r="D48" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>20</v>
+      </c>
+      <c r="B49" t="s">
+        <v>28</v>
+      </c>
+      <c r="C49" t="s">
+        <v>71</v>
+      </c>
+      <c r="D49" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>72</v>
+      </c>
+      <c r="B50" t="s">
+        <v>28</v>
+      </c>
+      <c r="C50" t="s">
+        <v>73</v>
+      </c>
+      <c r="D50" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>74</v>
+      </c>
+      <c r="B51" t="s">
+        <v>28</v>
+      </c>
+      <c r="C51" t="s">
+        <v>26</v>
+      </c>
+      <c r="D51" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B17:B23">
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C22:C23">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <dataValidations disablePrompts="1" count="6">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C35:C36" xr:uid="{806DEB49-2B61-4F7C-A4BD-A04E690DF9AD}">
+      <formula1>hid29den</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C3" xr:uid="{014D6161-32C2-4B77-B51A-637FAA6094C0}">
+      <formula1>hid1den</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C4" xr:uid="{8665F3BB-69CC-4B4E-85F7-9D917444E3AC}">
+      <formula1>hid2den</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C5" xr:uid="{7A95FC0D-5E36-4D78-B86B-AEA949E73984}">
+      <formula1>hid3den</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C6" xr:uid="{899B6F56-3346-4143-9C73-AE54F96D52E2}">
+      <formula1>hid4den</formula1>
+    </dataValidation>
+    <dataValidation type="list" showErrorMessage="1" sqref="C10:C13" xr:uid="{9511BE44-244D-4D78-AF14-2648978E7813}">
+      <formula1>hid23den</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/config/Ajio_dropdown.xlsx
+++ b/config/Ajio_dropdown.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\our data\KPA\NEW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABD5CBBD-F022-4C9F-98C7-F84F815C62EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49B768EA-0165-428C-8C10-6930E009CA28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="748" activeTab="1" xr2:uid="{C0D2C78A-6BFE-401C-9027-E5C9268B4C7B}"/>
   </bookViews>
@@ -16,14 +16,11 @@
     <sheet name="Dropdown-Tshirts" sheetId="5" r:id="rId1"/>
     <sheet name="Dropdown-Kids Tshirts" sheetId="6" r:id="rId2"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId3"/>
-  </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dropdown-Kids Tshirts'!$A$1:$D$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dropdown-Kids Tshirts'!$A$1:$D$63</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dropdown-Tshirts'!$A$1:$D$1</definedName>
     <definedName name="hid1den">#REF!</definedName>
-    <definedName name="hid23den">[1]sheetForStoringExtraValues!$X$1:$X$234</definedName>
+    <definedName name="hid23den">#REF!</definedName>
     <definedName name="hid29den">#REF!</definedName>
     <definedName name="hid2den">#REF!</definedName>
     <definedName name="hid3den">#REF!</definedName>
@@ -50,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="110">
   <si>
     <t>Blue</t>
   </si>
@@ -338,6 +335,48 @@
   </si>
   <si>
     <t>Ajio Category</t>
+  </si>
+  <si>
+    <t>Regular Machine Wash</t>
+  </si>
+  <si>
+    <t>Others</t>
+  </si>
+  <si>
+    <t>*Sleeve</t>
+  </si>
+  <si>
+    <t>Oversized Fit</t>
+  </si>
+  <si>
+    <t>Half Sleeves</t>
+  </si>
+  <si>
+    <t>Length</t>
+  </si>
+  <si>
+    <t>2-4Y</t>
+  </si>
+  <si>
+    <t>4-6Y</t>
+  </si>
+  <si>
+    <t>6-8Y</t>
+  </si>
+  <si>
+    <t>8-10Y</t>
+  </si>
+  <si>
+    <t>10-12Y</t>
+  </si>
+  <si>
+    <t>12-14Y</t>
+  </si>
+  <si>
+    <t>14-16Y</t>
+  </si>
+  <si>
+    <t>16-18Y</t>
   </si>
 </sst>
 </file>
@@ -439,1201 +478,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Template Instructions"/>
-      <sheetName val="Image Guidelines"/>
-      <sheetName val="sheetForStoringExtraValues"/>
-      <sheetName val="830501001_Styles_Tshirts"/>
-      <sheetName val="Seller Information Sheet"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2">
-        <row r="1">
-          <cell r="X1" t="str">
-            <v>Aladdin</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="X2" t="str">
-            <v>Angry Birds</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="X3" t="str">
-            <v>Barbie</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="X4" t="str">
-            <v>Ben 10</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="X5" t="str">
-            <v>Bob the Builder</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="X6" t="str">
-            <v>Bugs Bunny</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="X7" t="str">
-            <v>Captain America</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="X8" t="str">
-            <v>Chhota Bheem</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="X9" t="str">
-            <v>Chutki</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="X10" t="str">
-            <v>Cinderella</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="X11" t="str">
-            <v>DC Comics</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="X12" t="str">
-            <v>Deadpool</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="X13" t="str">
-            <v>Doctor Strange</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="X14" t="str">
-            <v>Donald Duck</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="X15" t="str">
-            <v>Dora</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="X16" t="str">
-            <v>Doremon</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="X17" t="str">
-            <v>DuckTales</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="X18" t="str">
-            <v>Frozen</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="X19" t="str">
-            <v>Genie</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="X20" t="str">
-            <v>Goku</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="X21" t="str">
-            <v>Goofy</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="X22" t="str">
-            <v>Groot</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="X23" t="str">
-            <v>Harry Potter</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="X24" t="str">
-            <v>Hello Kitty</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="X25" t="str">
-            <v>Hercules</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="X26" t="str">
-            <v>Hulk</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="X27" t="str">
-            <v>Iron Man</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="X28" t="str">
-            <v>Joker</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="X29" t="str">
-            <v>Jurassic World</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="X30" t="str">
-            <v>Kung Fu Panda</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="X31" t="str">
-            <v>Marvel</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="X32" t="str">
-            <v>Mickey Mouse</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="X33" t="str">
-            <v>Minions</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="X34" t="str">
-            <v>Motu Patlu</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="X35" t="str">
-            <v>Noddy</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="X36" t="str">
-            <v>Oggy and the Cockroaches</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="X37" t="str">
-            <v>Peter Pan</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="X38" t="str">
-            <v>Pluto</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="X39" t="str">
-            <v>Pokemon</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="X40" t="str">
-            <v>Popeye</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="X41" t="str">
-            <v>Scooby-Doo</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="X42" t="str">
-            <v>Shin-Chan</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="X43" t="str">
-            <v>Spider-Man</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="X44" t="str">
-            <v>SpongeBob SquarePants</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="X45" t="str">
-            <v>Star Trek</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="X46" t="str">
-            <v>Star Wars</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="X47" t="str">
-            <v>Superman</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="X48" t="str">
-            <v>Teenage Mutant Ninja Turtles</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="X49" t="str">
-            <v>The Avengers</v>
-          </cell>
-        </row>
-        <row r="50">
-          <cell r="X50" t="str">
-            <v>The Flash</v>
-          </cell>
-        </row>
-        <row r="51">
-          <cell r="X51" t="str">
-            <v>The Flintstones</v>
-          </cell>
-        </row>
-        <row r="52">
-          <cell r="X52" t="str">
-            <v>The Incredibles</v>
-          </cell>
-        </row>
-        <row r="53">
-          <cell r="X53" t="str">
-            <v>The Jungle Book</v>
-          </cell>
-        </row>
-        <row r="54">
-          <cell r="X54" t="str">
-            <v>The Little Mermaid</v>
-          </cell>
-        </row>
-        <row r="55">
-          <cell r="X55" t="str">
-            <v>The Powerpuff Girls</v>
-          </cell>
-        </row>
-        <row r="56">
-          <cell r="X56" t="str">
-            <v>Tinker Bell</v>
-          </cell>
-        </row>
-        <row r="57">
-          <cell r="X57" t="str">
-            <v>Tom and Jerry</v>
-          </cell>
-        </row>
-        <row r="58">
-          <cell r="X58" t="str">
-            <v>Transformers</v>
-          </cell>
-        </row>
-        <row r="59">
-          <cell r="X59" t="str">
-            <v>Winnie-the-Pooh</v>
-          </cell>
-        </row>
-        <row r="60">
-          <cell r="X60" t="str">
-            <v>Wolverine</v>
-          </cell>
-        </row>
-        <row r="61">
-          <cell r="X61" t="str">
-            <v>Wonder Woman</v>
-          </cell>
-        </row>
-        <row r="62">
-          <cell r="X62" t="str">
-            <v>WWE</v>
-          </cell>
-        </row>
-        <row r="63">
-          <cell r="X63" t="str">
-            <v>X-Men</v>
-          </cell>
-        </row>
-        <row r="64">
-          <cell r="X64" t="str">
-            <v>101 Dalmatians</v>
-          </cell>
-        </row>
-        <row r="65">
-          <cell r="X65" t="str">
-            <v>AC Milan</v>
-          </cell>
-        </row>
-        <row r="66">
-          <cell r="X66" t="str">
-            <v>AC/DC</v>
-          </cell>
-        </row>
-        <row r="67">
-          <cell r="X67" t="str">
-            <v>Annabelle</v>
-          </cell>
-        </row>
-        <row r="68">
-          <cell r="X68" t="str">
-            <v>Ant-Man</v>
-          </cell>
-        </row>
-        <row r="69">
-          <cell r="X69" t="str">
-            <v>Aquaman</v>
-          </cell>
-        </row>
-        <row r="70">
-          <cell r="X70" t="str">
-            <v>Archie</v>
-          </cell>
-        </row>
-        <row r="71">
-          <cell r="X71" t="str">
-            <v>Arrow</v>
-          </cell>
-        </row>
-        <row r="72">
-          <cell r="X72" t="str">
-            <v>Arsenal</v>
-          </cell>
-        </row>
-        <row r="73">
-          <cell r="X73" t="str">
-            <v>Attack on Titan</v>
-          </cell>
-        </row>
-        <row r="74">
-          <cell r="X74" t="str">
-            <v>Avatar</v>
-          </cell>
-        </row>
-        <row r="75">
-          <cell r="X75" t="str">
-            <v>Backstreet Boys</v>
-          </cell>
-        </row>
-        <row r="76">
-          <cell r="X76" t="str">
-            <v>Batman</v>
-          </cell>
-        </row>
-        <row r="77">
-          <cell r="X77" t="str">
-            <v>Bayern Munich</v>
-          </cell>
-        </row>
-        <row r="78">
-          <cell r="X78" t="str">
-            <v>Beach Boys</v>
-          </cell>
-        </row>
-        <row r="79">
-          <cell r="X79" t="str">
-            <v>Billie Eilish</v>
-          </cell>
-        </row>
-        <row r="80">
-          <cell r="X80" t="str">
-            <v>Blackpink</v>
-          </cell>
-        </row>
-        <row r="81">
-          <cell r="X81" t="str">
-            <v>BMW Motorsport</v>
-          </cell>
-        </row>
-        <row r="82">
-          <cell r="X82" t="str">
-            <v>Boston Celtics</v>
-          </cell>
-        </row>
-        <row r="83">
-          <cell r="X83" t="str">
-            <v>Breaking Bad</v>
-          </cell>
-        </row>
-        <row r="84">
-          <cell r="X84" t="str">
-            <v>Brooklyn Nets</v>
-          </cell>
-        </row>
-        <row r="85">
-          <cell r="X85" t="str">
-            <v>BTS</v>
-          </cell>
-        </row>
-        <row r="86">
-          <cell r="X86" t="str">
-            <v>Bubble Guppies</v>
-          </cell>
-        </row>
-        <row r="87">
-          <cell r="X87" t="str">
-            <v>Call of Duty</v>
-          </cell>
-        </row>
-        <row r="88">
-          <cell r="X88" t="str">
-            <v>Calvin &amp; Hobbes</v>
-          </cell>
-        </row>
-        <row r="89">
-          <cell r="X89" t="str">
-            <v>Cartoon Network</v>
-          </cell>
-        </row>
-        <row r="90">
-          <cell r="X90" t="str">
-            <v>Catwoman</v>
-          </cell>
-        </row>
-        <row r="91">
-          <cell r="X91" t="str">
-            <v>Che Guevara</v>
-          </cell>
-        </row>
-        <row r="92">
-          <cell r="X92" t="str">
-            <v>Chelsea</v>
-          </cell>
-        </row>
-        <row r="93">
-          <cell r="X93" t="str">
-            <v>Chennai Super Kings</v>
-          </cell>
-        </row>
-        <row r="94">
-          <cell r="X94" t="str">
-            <v>Chicago Bulls</v>
-          </cell>
-        </row>
-        <row r="95">
-          <cell r="X95" t="str">
-            <v>Clifford</v>
-          </cell>
-        </row>
-        <row r="96">
-          <cell r="X96" t="str">
-            <v>Coldplay</v>
-          </cell>
-        </row>
-        <row r="97">
-          <cell r="X97" t="str">
-            <v>Courage the Cowardly Dog</v>
-          </cell>
-        </row>
-        <row r="98">
-          <cell r="X98" t="str">
-            <v>Dallas Mavericks</v>
-          </cell>
-        </row>
-        <row r="99">
-          <cell r="X99" t="str">
-            <v>Daredevil</v>
-          </cell>
-        </row>
-        <row r="100">
-          <cell r="X100" t="str">
-            <v>Darth Vader</v>
-          </cell>
-        </row>
-        <row r="101">
-          <cell r="X101" t="str">
-            <v>DC Movie Universe</v>
-          </cell>
-        </row>
-        <row r="102">
-          <cell r="X102" t="str">
-            <v>Delhi Capitals</v>
-          </cell>
-        </row>
-        <row r="103">
-          <cell r="X103" t="str">
-            <v>Demon Slayer</v>
-          </cell>
-        </row>
-        <row r="104">
-          <cell r="X104" t="str">
-            <v>Dexter</v>
-          </cell>
-        </row>
-        <row r="105">
-          <cell r="X105" t="str">
-            <v>Diego</v>
-          </cell>
-        </row>
-        <row r="106">
-          <cell r="X106" t="str">
-            <v>Disney</v>
-          </cell>
-        </row>
-        <row r="107">
-          <cell r="X107" t="str">
-            <v>Dragon Ball Z</v>
-          </cell>
-        </row>
-        <row r="108">
-          <cell r="X108" t="str">
-            <v>Dragon Booster</v>
-          </cell>
-        </row>
-        <row r="109">
-          <cell r="X109" t="str">
-            <v>Eeyore</v>
-          </cell>
-        </row>
-        <row r="110">
-          <cell r="X110" t="str">
-            <v>Elvis Presley</v>
-          </cell>
-        </row>
-        <row r="111">
-          <cell r="X111" t="str">
-            <v>Eminem</v>
-          </cell>
-        </row>
-        <row r="112">
-          <cell r="X112" t="str">
-            <v>Eren</v>
-          </cell>
-        </row>
-        <row r="113">
-          <cell r="X113" t="str">
-            <v>Esports Teams</v>
-          </cell>
-        </row>
-        <row r="114">
-          <cell r="X114" t="str">
-            <v>Eternals</v>
-          </cell>
-        </row>
-        <row r="115">
-          <cell r="X115" t="str">
-            <v>Fantastic Beasts</v>
-          </cell>
-        </row>
-        <row r="116">
-          <cell r="X116" t="str">
-            <v>FC Barcelona</v>
-          </cell>
-        </row>
-        <row r="117">
-          <cell r="X117" t="str">
-            <v>Ferrari</v>
-          </cell>
-        </row>
-        <row r="118">
-          <cell r="X118" t="str">
-            <v>Fireman Sam</v>
-          </cell>
-        </row>
-        <row r="119">
-          <cell r="X119" t="str">
-            <v>Football Club Goa</v>
-          </cell>
-        </row>
-        <row r="120">
-          <cell r="X120" t="str">
-            <v>Formula 1</v>
-          </cell>
-        </row>
-        <row r="121">
-          <cell r="X121" t="str">
-            <v>Fortnite</v>
-          </cell>
-        </row>
-        <row r="122">
-          <cell r="X122" t="str">
-            <v>Free Fire</v>
-          </cell>
-        </row>
-        <row r="123">
-          <cell r="X123" t="str">
-            <v>G.I. Joe</v>
-          </cell>
-        </row>
-        <row r="124">
-          <cell r="X124" t="str">
-            <v>Ghost Rider</v>
-          </cell>
-        </row>
-        <row r="125">
-          <cell r="X125" t="str">
-            <v>Ghost Spider</v>
-          </cell>
-        </row>
-        <row r="126">
-          <cell r="X126" t="str">
-            <v>Godzilla</v>
-          </cell>
-        </row>
-        <row r="127">
-          <cell r="X127" t="str">
-            <v>Gojo</v>
-          </cell>
-        </row>
-        <row r="128">
-          <cell r="X128" t="str">
-            <v>Golden State Warriors</v>
-          </cell>
-        </row>
-        <row r="129">
-          <cell r="X129" t="str">
-            <v>Guardians of the Galaxy</v>
-          </cell>
-        </row>
-        <row r="130">
-          <cell r="X130" t="str">
-            <v>Gujarat Titans</v>
-          </cell>
-        </row>
-        <row r="131">
-          <cell r="X131" t="str">
-            <v>Guns N Roses</v>
-          </cell>
-        </row>
-        <row r="132">
-          <cell r="X132" t="str">
-            <v>Hannah Montana</v>
-          </cell>
-        </row>
-        <row r="133">
-          <cell r="X133" t="str">
-            <v>Hawkeye</v>
-          </cell>
-        </row>
-        <row r="134">
-          <cell r="X134" t="str">
-            <v>Hip Hop Icons</v>
-          </cell>
-        </row>
-        <row r="135">
-          <cell r="X135" t="str">
-            <v>Human Torch</v>
-          </cell>
-        </row>
-        <row r="136">
-          <cell r="X136" t="str">
-            <v>Indian Cricket Team</v>
-          </cell>
-        </row>
-        <row r="137">
-          <cell r="X137" t="str">
-            <v>Indiana Pacers</v>
-          </cell>
-        </row>
-        <row r="138">
-          <cell r="X138" t="str">
-            <v>Invisible Woman</v>
-          </cell>
-        </row>
-        <row r="139">
-          <cell r="X139" t="str">
-            <v>ISRO</v>
-          </cell>
-        </row>
-        <row r="140">
-          <cell r="X140" t="str">
-            <v>Itachi</v>
-          </cell>
-        </row>
-        <row r="141">
-          <cell r="X141" t="str">
-            <v>Johnny Bravo</v>
-          </cell>
-        </row>
-        <row r="142">
-          <cell r="X142" t="str">
-            <v>Jujutsu Kaisen</v>
-          </cell>
-        </row>
-        <row r="143">
-          <cell r="X143" t="str">
-            <v>Jurassic Park</v>
-          </cell>
-        </row>
-        <row r="144">
-          <cell r="X144" t="str">
-            <v>Juventus</v>
-          </cell>
-        </row>
-        <row r="145">
-          <cell r="X145" t="str">
-            <v>Ken</v>
-          </cell>
-        </row>
-        <row r="146">
-          <cell r="X146" t="str">
-            <v>Kolkata Knight Riders</v>
-          </cell>
-        </row>
-        <row r="147">
-          <cell r="X147" t="str">
-            <v>Kurt Cobain</v>
-          </cell>
-        </row>
-        <row r="148">
-          <cell r="X148" t="str">
-            <v>Levi</v>
-          </cell>
-        </row>
-        <row r="149">
-          <cell r="X149" t="str">
-            <v>Lilo &amp; Stitch</v>
-          </cell>
-        </row>
-        <row r="150">
-          <cell r="X150" t="str">
-            <v>Little Krishna</v>
-          </cell>
-        </row>
-        <row r="151">
-          <cell r="X151" t="str">
-            <v>Lord of the Rings</v>
-          </cell>
-        </row>
-        <row r="152">
-          <cell r="X152" t="str">
-            <v>Los Angeles Lakers</v>
-          </cell>
-        </row>
-        <row r="153">
-          <cell r="X153" t="str">
-            <v>Luffy</v>
-          </cell>
-        </row>
-        <row r="154">
-          <cell r="X154" t="str">
-            <v>Madagascar</v>
-          </cell>
-        </row>
-        <row r="155">
-          <cell r="X155" t="str">
-            <v>Manchester City</v>
-          </cell>
-        </row>
-        <row r="156">
-          <cell r="X156" t="str">
-            <v>Manchester United</v>
-          </cell>
-        </row>
-        <row r="157">
-          <cell r="X157" t="str">
-            <v>Max &amp; Ruby</v>
-          </cell>
-        </row>
-        <row r="158">
-          <cell r="X158" t="str">
-            <v>Mercedes-AMG Petronas</v>
-          </cell>
-        </row>
-        <row r="159">
-          <cell r="X159" t="str">
-            <v>Miami Heat</v>
-          </cell>
-        </row>
-        <row r="160">
-          <cell r="X160" t="str">
-            <v>Michael Jordan</v>
-          </cell>
-        </row>
-        <row r="161">
-          <cell r="X161" t="str">
-            <v>Minnie Mouse</v>
-          </cell>
-        </row>
-        <row r="162">
-          <cell r="X162" t="str">
-            <v>Mister Fantastic</v>
-          </cell>
-        </row>
-        <row r="163">
-          <cell r="X163" t="str">
-            <v>Money Heist</v>
-          </cell>
-        </row>
-        <row r="164">
-          <cell r="X164" t="str">
-            <v>Monsters Inc.</v>
-          </cell>
-        </row>
-        <row r="165">
-          <cell r="X165" t="str">
-            <v>Mortal Kombat</v>
-          </cell>
-        </row>
-        <row r="166">
-          <cell r="X166" t="str">
-            <v>MotoGP</v>
-          </cell>
-        </row>
-        <row r="167">
-          <cell r="X167" t="str">
-            <v>Mr Bean</v>
-          </cell>
-        </row>
-        <row r="168">
-          <cell r="X168" t="str">
-            <v>Mumbai Indians</v>
-          </cell>
-        </row>
-        <row r="169">
-          <cell r="X169" t="str">
-            <v>My Little Pony</v>
-          </cell>
-        </row>
-        <row r="170">
-          <cell r="X170" t="str">
-            <v>Naruto</v>
-          </cell>
-        </row>
-        <row r="171">
-          <cell r="X171" t="str">
-            <v>NASA</v>
-          </cell>
-        </row>
-        <row r="172">
-          <cell r="X172" t="str">
-            <v>NBA</v>
-          </cell>
-        </row>
-        <row r="173">
-          <cell r="X173" t="str">
-            <v>Nemo</v>
-          </cell>
-        </row>
-        <row r="174">
-          <cell r="X174" t="str">
-            <v>New Orleans Pelicans</v>
-          </cell>
-        </row>
-        <row r="175">
-          <cell r="X175" t="str">
-            <v>New York Knicks</v>
-          </cell>
-        </row>
-        <row r="176">
-          <cell r="X176" t="str">
-            <v>Nezuko</v>
-          </cell>
-        </row>
-        <row r="177">
-          <cell r="X177" t="str">
-            <v>Ninja Hattori</v>
-          </cell>
-        </row>
-        <row r="178">
-          <cell r="X178" t="str">
-            <v>Nirvana</v>
-          </cell>
-        </row>
-        <row r="179">
-          <cell r="X179" t="str">
-            <v>One Piece</v>
-          </cell>
-        </row>
-        <row r="180">
-          <cell r="X180" t="str">
-            <v>Others</v>
-          </cell>
-        </row>
-        <row r="181">
-          <cell r="X181" t="str">
-            <v>Outlander</v>
-          </cell>
-        </row>
-        <row r="182">
-          <cell r="X182" t="str">
-            <v>Paris Saint-Germain</v>
-          </cell>
-        </row>
-        <row r="183">
-          <cell r="X183" t="str">
-            <v>PAW Patrol</v>
-          </cell>
-        </row>
-        <row r="184">
-          <cell r="X184" t="str">
-            <v>Peanuts</v>
-          </cell>
-        </row>
-        <row r="185">
-          <cell r="X185" t="str">
-            <v>Phineas and Ferb</v>
-          </cell>
-        </row>
-        <row r="186">
-          <cell r="X186" t="str">
-            <v>Pink Floyd</v>
-          </cell>
-        </row>
-        <row r="187">
-          <cell r="X187" t="str">
-            <v>Pixar</v>
-          </cell>
-        </row>
-        <row r="188">
-          <cell r="X188" t="str">
-            <v>Porsche</v>
-          </cell>
-        </row>
-        <row r="189">
-          <cell r="X189" t="str">
-            <v>Power Rangers</v>
-          </cell>
-        </row>
-        <row r="190">
-          <cell r="X190" t="str">
-            <v>PUBG</v>
-          </cell>
-        </row>
-        <row r="191">
-          <cell r="X191" t="str">
-            <v>Punisher</v>
-          </cell>
-        </row>
-        <row r="192">
-          <cell r="X192" t="str">
-            <v>Punjab Kings</v>
-          </cell>
-        </row>
-        <row r="193">
-          <cell r="X193" t="str">
-            <v>Real Madrid</v>
-          </cell>
-        </row>
-        <row r="194">
-          <cell r="X194" t="str">
-            <v>Red Bull Racing</v>
-          </cell>
-        </row>
-        <row r="195">
-          <cell r="X195" t="str">
-            <v>Royal Challengers</v>
-          </cell>
-        </row>
-        <row r="196">
-          <cell r="X196" t="str">
-            <v>Sasuke</v>
-          </cell>
-        </row>
-        <row r="197">
-          <cell r="X197" t="str">
-            <v>Sesame Street</v>
-          </cell>
-        </row>
-        <row r="198">
-          <cell r="X198" t="str">
-            <v>Shaun the Sheep</v>
-          </cell>
-        </row>
-        <row r="199">
-          <cell r="X199" t="str">
-            <v>Sheriff Callie's Wild West</v>
-          </cell>
-        </row>
-        <row r="200">
-          <cell r="X200" t="str">
-            <v>Sherlock</v>
-          </cell>
-        </row>
-        <row r="201">
-          <cell r="X201" t="str">
-            <v>Shiva</v>
-          </cell>
-        </row>
-        <row r="202">
-          <cell r="X202" t="str">
-            <v>Silver Surfer</v>
-          </cell>
-        </row>
-        <row r="203">
-          <cell r="X203" t="str">
-            <v>Simba</v>
-          </cell>
-        </row>
-        <row r="204">
-          <cell r="X204" t="str">
-            <v>Snoopy</v>
-          </cell>
-        </row>
-        <row r="205">
-          <cell r="X205" t="str">
-            <v>Sofia the First</v>
-          </cell>
-        </row>
-        <row r="206">
-          <cell r="X206" t="str">
-            <v>Squid Game</v>
-          </cell>
-        </row>
-        <row r="207">
-          <cell r="X207" t="str">
-            <v>Storm</v>
-          </cell>
-        </row>
-        <row r="208">
-          <cell r="X208" t="str">
-            <v>Street Fighter</v>
-          </cell>
-        </row>
-        <row r="209">
-          <cell r="X209" t="str">
-            <v>Sukuna</v>
-          </cell>
-        </row>
-        <row r="210">
-          <cell r="X210" t="str">
-            <v>Sunrisers Hyderabad</v>
-          </cell>
-        </row>
-        <row r="211">
-          <cell r="X211" t="str">
-            <v>Super Mario</v>
-          </cell>
-        </row>
-        <row r="212">
-          <cell r="X212" t="str">
-            <v>Super Spy</v>
-          </cell>
-        </row>
-        <row r="213">
-          <cell r="X213" t="str">
-            <v>SWAT Kats</v>
-          </cell>
-        </row>
-        <row r="214">
-          <cell r="X214" t="str">
-            <v>Sylvester</v>
-          </cell>
-        </row>
-        <row r="215">
-          <cell r="X215" t="str">
-            <v>Taylor Swift</v>
-          </cell>
-        </row>
-        <row r="216">
-          <cell r="X216" t="str">
-            <v>Team Umizoomi</v>
-          </cell>
-        </row>
-        <row r="217">
-          <cell r="X217" t="str">
-            <v>The Beatles</v>
-          </cell>
-        </row>
-        <row r="218">
-          <cell r="X218" t="str">
-            <v>The Boys</v>
-          </cell>
-        </row>
-        <row r="219">
-          <cell r="X219" t="str">
-            <v>The Pink Panther</v>
-          </cell>
-        </row>
-        <row r="220">
-          <cell r="X220" t="str">
-            <v>The Rolling Stones</v>
-          </cell>
-        </row>
-        <row r="221">
-          <cell r="X221" t="str">
-            <v>The Simpsons</v>
-          </cell>
-        </row>
-        <row r="222">
-          <cell r="X222" t="str">
-            <v>The Weeknd</v>
-          </cell>
-        </row>
-        <row r="223">
-          <cell r="X223" t="str">
-            <v>Thomas &amp; Friends</v>
-          </cell>
-        </row>
-        <row r="224">
-          <cell r="X224" t="str">
-            <v>Thor</v>
-          </cell>
-        </row>
-        <row r="225">
-          <cell r="X225" t="str">
-            <v>Tiger King</v>
-          </cell>
-        </row>
-        <row r="226">
-          <cell r="X226" t="str">
-            <v>Toy Story</v>
-          </cell>
-        </row>
-        <row r="227">
-          <cell r="X227" t="str">
-            <v>Travis Scott</v>
-          </cell>
-        </row>
-        <row r="228">
-          <cell r="X228" t="str">
-            <v>Tweetie Pie</v>
-          </cell>
-        </row>
-        <row r="229">
-          <cell r="X229" t="str">
-            <v>Vegeta</v>
-          </cell>
-        </row>
-        <row r="230">
-          <cell r="X230" t="str">
-            <v>Venom</v>
-          </cell>
-        </row>
-        <row r="231">
-          <cell r="X231" t="str">
-            <v>We Bare Bears</v>
-          </cell>
-        </row>
-        <row r="232">
-          <cell r="X232" t="str">
-            <v>Winx Club</v>
-          </cell>
-        </row>
-        <row r="233">
-          <cell r="X233" t="str">
-            <v>Zenitsu</v>
-          </cell>
-        </row>
-        <row r="234">
-          <cell r="X234" t="str">
-            <v>Zoro</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2570,7 +1414,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5E74C28-9494-4104-81C6-5A34A8ECDBE0}">
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D65"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.453125" bestFit="1" customWidth="1"/>
@@ -2683,6 +1527,9 @@
       <c r="B8" t="s">
         <v>48</v>
       </c>
+      <c r="C8" t="s">
+        <v>97</v>
+      </c>
       <c r="D8" t="s">
         <v>28</v>
       </c>
@@ -2694,6 +1541,9 @@
       <c r="B9" t="s">
         <v>75</v>
       </c>
+      <c r="C9" t="s">
+        <v>97</v>
+      </c>
       <c r="D9" t="s">
         <v>28</v>
       </c>
@@ -2756,13 +1606,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>50</v>
-      </c>
-      <c r="B14" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="C14" t="s">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="D14" t="s">
         <v>28</v>
@@ -2770,13 +1617,13 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>51</v>
-      </c>
-      <c r="B15">
-        <v>1</v>
+        <v>50</v>
+      </c>
+      <c r="B15" t="s">
+        <v>28</v>
       </c>
       <c r="C15" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D15" t="s">
         <v>28</v>
@@ -2787,10 +1634,10 @@
         <v>51</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D16" t="s">
         <v>28</v>
@@ -2798,13 +1645,13 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>52</v>
-      </c>
-      <c r="B17" t="s">
+        <v>51</v>
+      </c>
+      <c r="B17">
         <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="D17" t="s">
         <v>28</v>
@@ -2815,10 +1662,10 @@
         <v>52</v>
       </c>
       <c r="B18" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D18" t="s">
         <v>28</v>
@@ -2829,10 +1676,10 @@
         <v>52</v>
       </c>
       <c r="B19" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C19" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" t="s">
         <v>28</v>
@@ -2843,10 +1690,10 @@
         <v>52</v>
       </c>
       <c r="B20" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D20" t="s">
         <v>28</v>
@@ -2857,10 +1704,10 @@
         <v>52</v>
       </c>
       <c r="B21" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C21" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D21" t="s">
         <v>28</v>
@@ -2871,10 +1718,10 @@
         <v>52</v>
       </c>
       <c r="B22" t="s">
-        <v>82</v>
+        <v>3</v>
       </c>
       <c r="C22" t="s">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="D22" t="s">
         <v>28</v>
@@ -2885,10 +1732,10 @@
         <v>52</v>
       </c>
       <c r="B23" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C23" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D23" t="s">
         <v>28</v>
@@ -2896,13 +1743,13 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B24" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="C24" t="s">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="D24" t="s">
         <v>28</v>
@@ -2913,7 +1760,7 @@
         <v>53</v>
       </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>31</v>
       </c>
       <c r="C25" t="s">
         <v>17</v>
@@ -2924,13 +1771,13 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="C26" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="D26" t="s">
         <v>28</v>
@@ -2941,7 +1788,7 @@
         <v>54</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C27" t="s">
         <v>55</v>
@@ -2952,13 +1799,13 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C28" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D28" t="s">
         <v>28</v>
@@ -2966,13 +1813,13 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B29" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="C29" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D29" t="s">
         <v>28</v>
@@ -2980,13 +1827,13 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B30" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="C30" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="D30" t="s">
         <v>28</v>
@@ -2994,13 +1841,13 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B31" t="s">
-        <v>28</v>
+        <v>96</v>
       </c>
       <c r="C31" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D31" t="s">
         <v>28</v>
@@ -3008,13 +1855,13 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B32" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C32" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="D32" t="s">
         <v>28</v>
@@ -3022,13 +1869,13 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B33" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C33" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D33" t="s">
         <v>28</v>
@@ -3036,13 +1883,13 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B34" t="s">
-        <v>19</v>
+        <v>99</v>
       </c>
       <c r="C34" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="D34" t="s">
         <v>28</v>
@@ -3050,13 +1897,13 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>66</v>
-      </c>
-      <c r="B35">
-        <v>1</v>
+        <v>62</v>
+      </c>
+      <c r="B35" t="s">
+        <v>28</v>
       </c>
       <c r="C35" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D35" t="s">
         <v>28</v>
@@ -3064,13 +1911,13 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>66</v>
-      </c>
-      <c r="B36">
-        <v>2</v>
+        <v>101</v>
+      </c>
+      <c r="B36" t="s">
+        <v>21</v>
       </c>
       <c r="C36" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="D36" t="s">
         <v>28</v>
@@ -3078,13 +1925,13 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>32</v>
+        <v>101</v>
       </c>
       <c r="B37" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C37" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D37" t="s">
         <v>28</v>
@@ -3092,13 +1939,13 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B38" t="s">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="C38" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="D38" t="s">
         <v>28</v>
@@ -3106,13 +1953,13 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>69</v>
-      </c>
-      <c r="B39" t="s">
-        <v>86</v>
+        <v>66</v>
+      </c>
+      <c r="B39">
+        <v>1</v>
       </c>
       <c r="C39" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="D39" t="s">
         <v>28</v>
@@ -3120,13 +1967,13 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>69</v>
-      </c>
-      <c r="B40" t="s">
-        <v>87</v>
+        <v>66</v>
+      </c>
+      <c r="B40">
+        <v>2</v>
       </c>
       <c r="C40" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="D40" t="s">
         <v>28</v>
@@ -3134,13 +1981,13 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="B41" t="s">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="C41" t="s">
-        <v>88</v>
+        <v>33</v>
       </c>
       <c r="D41" t="s">
         <v>28</v>
@@ -3151,10 +1998,10 @@
         <v>69</v>
       </c>
       <c r="B42" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C42" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D42" t="s">
         <v>28</v>
@@ -3165,10 +2012,10 @@
         <v>69</v>
       </c>
       <c r="B43" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C43" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D43" t="s">
         <v>28</v>
@@ -3179,10 +2026,10 @@
         <v>69</v>
       </c>
       <c r="B44" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C44" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D44" t="s">
         <v>28</v>
@@ -3193,10 +2040,10 @@
         <v>69</v>
       </c>
       <c r="B45" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C45" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D45" t="s">
         <v>28</v>
@@ -3207,10 +2054,10 @@
         <v>69</v>
       </c>
       <c r="B46" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C46" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D46" t="s">
         <v>28</v>
@@ -3221,10 +2068,10 @@
         <v>69</v>
       </c>
       <c r="B47" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C47" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D47" t="s">
         <v>28</v>
@@ -3232,13 +2079,13 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B48" t="s">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="C48" t="s">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="D48" t="s">
         <v>28</v>
@@ -3246,13 +2093,13 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="B49" t="s">
-        <v>28</v>
+        <v>92</v>
       </c>
       <c r="C49" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="D49" t="s">
         <v>28</v>
@@ -3260,13 +2107,13 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B50" t="s">
-        <v>28</v>
+        <v>93</v>
       </c>
       <c r="C50" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="D50" t="s">
         <v>28</v>
@@ -3274,27 +2121,223 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
+        <v>69</v>
+      </c>
+      <c r="B51" t="s">
+        <v>94</v>
+      </c>
+      <c r="C51" t="s">
+        <v>94</v>
+      </c>
+      <c r="D51" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>69</v>
+      </c>
+      <c r="B52" t="s">
+        <v>102</v>
+      </c>
+      <c r="C52" t="s">
+        <v>102</v>
+      </c>
+      <c r="D52" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>69</v>
+      </c>
+      <c r="B53" t="s">
+        <v>103</v>
+      </c>
+      <c r="C53" t="s">
+        <v>103</v>
+      </c>
+      <c r="D53" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>69</v>
+      </c>
+      <c r="B54" t="s">
+        <v>104</v>
+      </c>
+      <c r="C54" t="s">
+        <v>104</v>
+      </c>
+      <c r="D54" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>69</v>
+      </c>
+      <c r="B55" t="s">
+        <v>105</v>
+      </c>
+      <c r="C55" t="s">
+        <v>105</v>
+      </c>
+      <c r="D55" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>69</v>
+      </c>
+      <c r="B56" t="s">
+        <v>106</v>
+      </c>
+      <c r="C56" t="s">
+        <v>106</v>
+      </c>
+      <c r="D56" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>69</v>
+      </c>
+      <c r="B57" t="s">
+        <v>107</v>
+      </c>
+      <c r="C57" t="s">
+        <v>107</v>
+      </c>
+      <c r="D57" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>69</v>
+      </c>
+      <c r="B58" t="s">
+        <v>108</v>
+      </c>
+      <c r="C58" t="s">
+        <v>108</v>
+      </c>
+      <c r="D58" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>69</v>
+      </c>
+      <c r="B59" t="s">
+        <v>109</v>
+      </c>
+      <c r="C59" t="s">
+        <v>109</v>
+      </c>
+      <c r="D59" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>70</v>
+      </c>
+      <c r="B60" t="s">
+        <v>19</v>
+      </c>
+      <c r="C60" t="s">
+        <v>65</v>
+      </c>
+      <c r="D60" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>20</v>
+      </c>
+      <c r="B61" t="s">
+        <v>28</v>
+      </c>
+      <c r="C61" t="s">
+        <v>71</v>
+      </c>
+      <c r="D61" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>72</v>
+      </c>
+      <c r="B62" t="s">
+        <v>28</v>
+      </c>
+      <c r="C62" t="s">
+        <v>73</v>
+      </c>
+      <c r="D62" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
         <v>74</v>
       </c>
-      <c r="B51" t="s">
-        <v>28</v>
-      </c>
-      <c r="C51" t="s">
+      <c r="B63" t="s">
+        <v>28</v>
+      </c>
+      <c r="C63" t="s">
         <v>26</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D63" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>98</v>
+      </c>
+      <c r="B64" t="s">
+        <v>18</v>
+      </c>
+      <c r="C64" t="s">
+        <v>25</v>
+      </c>
+      <c r="D64" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>98</v>
+      </c>
+      <c r="B65" t="s">
+        <v>100</v>
+      </c>
+      <c r="C65" t="s">
+        <v>25</v>
+      </c>
+      <c r="D65" t="s">
         <v>28</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B17:B23">
+  <conditionalFormatting sqref="B18:B24">
     <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C22:C23">
+  <conditionalFormatting sqref="C23:C24">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="6">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C35:C36" xr:uid="{806DEB49-2B61-4F7C-A4BD-A04E690DF9AD}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C39:C40" xr:uid="{806DEB49-2B61-4F7C-A4BD-A04E690DF9AD}">
       <formula1>hid29den</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C3" xr:uid="{014D6161-32C2-4B77-B51A-637FAA6094C0}">
@@ -3309,7 +2352,7 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C6" xr:uid="{899B6F56-3346-4143-9C73-AE54F96D52E2}">
       <formula1>hid4den</formula1>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" sqref="C10:C13" xr:uid="{9511BE44-244D-4D78-AF14-2648978E7813}">
+    <dataValidation type="list" showErrorMessage="1" sqref="C10:C14" xr:uid="{9511BE44-244D-4D78-AF14-2648978E7813}">
       <formula1>hid23den</formula1>
     </dataValidation>
   </dataValidations>

--- a/config/Ajio_dropdown.xlsx
+++ b/config/Ajio_dropdown.xlsx
@@ -8,22 +8,31 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\our data\KPA\NEW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49B768EA-0165-428C-8C10-6930E009CA28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C90A248-8AB4-46EE-89B9-DA07E46C0D7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="748" activeTab="1" xr2:uid="{C0D2C78A-6BFE-401C-9027-E5C9268B4C7B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="748" activeTab="3" xr2:uid="{C0D2C78A-6BFE-401C-9027-E5C9268B4C7B}"/>
   </bookViews>
   <sheets>
     <sheet name="Dropdown-Tshirts" sheetId="5" r:id="rId1"/>
     <sheet name="Dropdown-Kids Tshirts" sheetId="6" r:id="rId2"/>
+    <sheet name="Dropdown-Boys Sandal" sheetId="7" r:id="rId3"/>
+    <sheet name="Dropdown-Boys Shoes" sheetId="8" r:id="rId4"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId5"/>
+  </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dropdown-Kids Tshirts'!$A$1:$D$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dropdown-Kids Tshirts'!$A$1:$D$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dropdown-Tshirts'!$A$1:$D$1</definedName>
+    <definedName name="hid16den">[1]sheetForStoringExtraValues!$Q$1:$Q$25</definedName>
+    <definedName name="hid17den">[1]sheetForStoringExtraValues!$R$1:$R$18</definedName>
     <definedName name="hid1den">#REF!</definedName>
     <definedName name="hid23den">#REF!</definedName>
+    <definedName name="hid25den">[1]sheetForStoringExtraValues!$Z$1:$Z$5</definedName>
     <definedName name="hid29den">#REF!</definedName>
     <definedName name="hid2den">#REF!</definedName>
     <definedName name="hid3den">#REF!</definedName>
+    <definedName name="hid46den">[1]sheetForStoringExtraValues!$AU$1:$AU$25</definedName>
     <definedName name="hid4den">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -47,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="185">
   <si>
     <t>Blue</t>
   </si>
@@ -377,6 +386,231 @@
   </si>
   <si>
     <t>16-18Y</t>
+  </si>
+  <si>
+    <t>Machine Wash. Dry Inside Out, In Shade.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Graphic </t>
+  </si>
+  <si>
+    <t>Typography</t>
+  </si>
+  <si>
+    <t>Typographic</t>
+  </si>
+  <si>
+    <t>Boys Sandal</t>
+  </si>
+  <si>
+    <t>Fashion</t>
+  </si>
+  <si>
+    <t>*articleDimensionsUnitHeight</t>
+  </si>
+  <si>
+    <t>*articleDimensionsUnitLength</t>
+  </si>
+  <si>
+    <t>*articleDimensionsUnitWidth</t>
+  </si>
+  <si>
+    <t>*articleDimensionsUnitLengthUOM</t>
+  </si>
+  <si>
+    <t>CM</t>
+  </si>
+  <si>
+    <t>*articleDimensionsUnitWeight</t>
+  </si>
+  <si>
+    <t>*articleDimensionsUnitWeightUOM</t>
+  </si>
+  <si>
+    <t>GRAM</t>
+  </si>
+  <si>
+    <t>*packageDimensionsHeight</t>
+  </si>
+  <si>
+    <t>*packageDimensionsLength</t>
+  </si>
+  <si>
+    <t>*packageDimensionsWidth</t>
+  </si>
+  <si>
+    <t>*packageDimensionsLengthUOM</t>
+  </si>
+  <si>
+    <t>*packageDimensionsWeight</t>
+  </si>
+  <si>
+    <t>*packageDimensionsWeightUOM</t>
+  </si>
+  <si>
+    <t>*Component Count</t>
+  </si>
+  <si>
+    <t>Smart Casual</t>
+  </si>
+  <si>
+    <t>Fit Type</t>
+  </si>
+  <si>
+    <t>*Care</t>
+  </si>
+  <si>
+    <t>Wipe with a clean, dry cloth when needed</t>
+  </si>
+  <si>
+    <t>*Heel</t>
+  </si>
+  <si>
+    <t>Stacked</t>
+  </si>
+  <si>
+    <t>*Toe-shape</t>
+  </si>
+  <si>
+    <t>Shoes</t>
+  </si>
+  <si>
+    <t>Silver</t>
+  </si>
+  <si>
+    <t>Green</t>
+  </si>
+  <si>
+    <t>Navy Blue</t>
+  </si>
+  <si>
+    <t>Navy</t>
+  </si>
+  <si>
+    <t>Purple</t>
+  </si>
+  <si>
+    <t>Brown</t>
+  </si>
+  <si>
+    <t>Cream</t>
+  </si>
+  <si>
+    <t>Mauve</t>
+  </si>
+  <si>
+    <t>*Upper Material</t>
+  </si>
+  <si>
+    <t>Synthetic</t>
+  </si>
+  <si>
+    <t>Synthetic upper</t>
+  </si>
+  <si>
+    <t>EVA</t>
+  </si>
+  <si>
+    <t>EVA upper</t>
+  </si>
+  <si>
+    <t>RUBBER</t>
+  </si>
+  <si>
+    <t>Rubber upper</t>
+  </si>
+  <si>
+    <t>*Sole Material</t>
+  </si>
+  <si>
+    <t>TPR</t>
+  </si>
+  <si>
+    <t>TPR sole</t>
+  </si>
+  <si>
+    <t>Rubber sole</t>
+  </si>
+  <si>
+    <t>*Fastening</t>
+  </si>
+  <si>
+    <t>Velcro</t>
+  </si>
+  <si>
+    <t>Velcro fastening</t>
+  </si>
+  <si>
+    <t>Slip-On</t>
+  </si>
+  <si>
+    <t>Slip-on styling</t>
+  </si>
+  <si>
+    <t>Snap Button</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>6-9M</t>
+  </si>
+  <si>
+    <t>9-12M</t>
+  </si>
+  <si>
+    <t>12-15M</t>
+  </si>
+  <si>
+    <t>15-18M</t>
+  </si>
+  <si>
+    <t>18-24M</t>
+  </si>
+  <si>
+    <t>2-2.5Y</t>
+  </si>
+  <si>
+    <t>2.5-3Y</t>
+  </si>
+  <si>
+    <t>3-3.5Y</t>
+  </si>
+  <si>
+    <t>3.5-4Y</t>
+  </si>
+  <si>
+    <t>4-4.5Y</t>
+  </si>
+  <si>
+    <t>4.5-5Y</t>
+  </si>
+  <si>
+    <t>5-5.5Y</t>
+  </si>
+  <si>
+    <t>18-21M</t>
+  </si>
+  <si>
+    <t>21-24M</t>
+  </si>
+  <si>
+    <t>12-18M</t>
+  </si>
+  <si>
+    <t>3-6M</t>
+  </si>
+  <si>
+    <t>Boys Shoes</t>
+  </si>
+  <si>
+    <t>Ankle Style</t>
+  </si>
+  <si>
+    <t>Mid-Tops</t>
+  </si>
+  <si>
+    <t>Slip-ons</t>
   </si>
 </sst>
 </file>
@@ -437,10 +671,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -478,6 +715,305 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Template Instructions"/>
+      <sheetName val="Image Guidelines"/>
+      <sheetName val="sheetForStoringExtraValues"/>
+      <sheetName val="830508004_Styles_Shoes"/>
+      <sheetName val="830508002_Styles_Sandals"/>
+      <sheetName val="Seller Information Sheet"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2">
+        <row r="1">
+          <cell r="F1" t="str">
+            <v>CM</v>
+          </cell>
+          <cell r="Q1" t="str">
+            <v>Canvas upper</v>
+          </cell>
+          <cell r="R1" t="str">
+            <v>Cork sole</v>
+          </cell>
+          <cell r="Z1" t="str">
+            <v>Slip-ons</v>
+          </cell>
+          <cell r="AU1" t="str">
+            <v>Canvas upper</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="Q2" t="str">
+            <v>EVA upper</v>
+          </cell>
+          <cell r="R2" t="str">
+            <v>Croslite sole</v>
+          </cell>
+          <cell r="Z2" t="str">
+            <v>Oxfords</v>
+          </cell>
+          <cell r="AU2" t="str">
+            <v>EVA upper</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="Q3" t="str">
+            <v>Fabric upper</v>
+          </cell>
+          <cell r="R3" t="str">
+            <v>Leather sole</v>
+          </cell>
+          <cell r="Z3" t="str">
+            <v>Derby</v>
+          </cell>
+          <cell r="AU3" t="str">
+            <v>Fabric upper</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="Q4" t="str">
+            <v>Genuine leather upper</v>
+          </cell>
+          <cell r="R4" t="str">
+            <v>Neolite sole</v>
+          </cell>
+          <cell r="Z4" t="str">
+            <v>Boots</v>
+          </cell>
+          <cell r="AU4" t="str">
+            <v>Genuine leather upper</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="Q5" t="str">
+            <v>Jute upper</v>
+          </cell>
+          <cell r="R5" t="str">
+            <v>PU sole</v>
+          </cell>
+          <cell r="Z5" t="str">
+            <v>Lace-Ups</v>
+          </cell>
+          <cell r="AU5" t="str">
+            <v>Jute upper</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="Q6" t="str">
+            <v>Knitted upper</v>
+          </cell>
+          <cell r="R6" t="str">
+            <v>PVC sole</v>
+          </cell>
+          <cell r="AU6" t="str">
+            <v>Knitted upper</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="Q7" t="str">
+            <v>Mesh upper</v>
+          </cell>
+          <cell r="R7" t="str">
+            <v>Resin sole</v>
+          </cell>
+          <cell r="AU7" t="str">
+            <v>Mesh upper</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="Q8" t="str">
+            <v>Polyester upper</v>
+          </cell>
+          <cell r="R8" t="str">
+            <v>Rubber sole</v>
+          </cell>
+          <cell r="AU8" t="str">
+            <v>Polyester upper</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="Q9" t="str">
+            <v>PU upper</v>
+          </cell>
+          <cell r="R9" t="str">
+            <v>TPR sole</v>
+          </cell>
+          <cell r="AU9" t="str">
+            <v>PU upper</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="Q10" t="str">
+            <v>PVC upper</v>
+          </cell>
+          <cell r="R10" t="str">
+            <v>TPU sole</v>
+          </cell>
+          <cell r="AU10" t="str">
+            <v>PVC upper</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="Q11" t="str">
+            <v>Rexene upper</v>
+          </cell>
+          <cell r="R11" t="str">
+            <v>Tunit sole</v>
+          </cell>
+          <cell r="AU11" t="str">
+            <v>Rexene upper</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="Q12" t="str">
+            <v>Rubber upper</v>
+          </cell>
+          <cell r="R12" t="str">
+            <v>Synthetic sole</v>
+          </cell>
+          <cell r="AU12" t="str">
+            <v>Rubber upper</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="Q13" t="str">
+            <v>Satin upper</v>
+          </cell>
+          <cell r="R13" t="str">
+            <v>Polyester sole</v>
+          </cell>
+          <cell r="AU13" t="str">
+            <v>Satin upper</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="Q14" t="str">
+            <v>Suede upper</v>
+          </cell>
+          <cell r="R14" t="str">
+            <v>Fabric sole</v>
+          </cell>
+          <cell r="AU14" t="str">
+            <v>Suede upper</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="Q15" t="str">
+            <v>Synthetic upper</v>
+          </cell>
+          <cell r="R15" t="str">
+            <v>Latex sole</v>
+          </cell>
+          <cell r="AU15" t="str">
+            <v>Synthetic upper</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="Q16" t="str">
+            <v>Velvet upper</v>
+          </cell>
+          <cell r="R16" t="str">
+            <v>Hyper Burst sole</v>
+          </cell>
+          <cell r="AU16" t="str">
+            <v>Velvet upper</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="Q17" t="str">
+            <v>Denim upper</v>
+          </cell>
+          <cell r="R17" t="str">
+            <v>Ultra Flight sole</v>
+          </cell>
+          <cell r="AU17" t="str">
+            <v>Denim upper</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="Q18" t="str">
+            <v>Faux leather upper</v>
+          </cell>
+          <cell r="R18" t="str">
+            <v>Ultra Go sole</v>
+          </cell>
+          <cell r="AU18" t="str">
+            <v>Faux leather upper</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="Q19" t="str">
+            <v>Lace upper</v>
+          </cell>
+          <cell r="AU19" t="str">
+            <v>Lace upper</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="Q20" t="str">
+            <v>Nubuck upper</v>
+          </cell>
+          <cell r="AU20" t="str">
+            <v>Nubuck upper</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="Q21" t="str">
+            <v>Patent leather upper</v>
+          </cell>
+          <cell r="AU21" t="str">
+            <v>Patent leather upper</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="Q22" t="str">
+            <v>Synthetic fibre upper</v>
+          </cell>
+          <cell r="AU22" t="str">
+            <v>Synthetic fibre upper</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="Q23" t="str">
+            <v>Tweed upper</v>
+          </cell>
+          <cell r="AU23" t="str">
+            <v>Tweed upper</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="Q24" t="str">
+            <v>Wool upper</v>
+          </cell>
+          <cell r="AU24" t="str">
+            <v>Wool upper</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="Q25" t="str">
+            <v>Textile</v>
+          </cell>
+          <cell r="AU25" t="str">
+            <v>Textile</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -797,7 +1333,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93FEB0F0-8794-4F72-85E1-24AFD1DB4E9B}">
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.453125" bestFit="1" customWidth="1"/>
@@ -1070,13 +1606,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="C20" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D20" t="s">
         <v>28</v>
@@ -1084,13 +1620,13 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="C21" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="D21" t="s">
         <v>28</v>
@@ -1098,13 +1634,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B22" t="s">
-        <v>37</v>
+        <v>111</v>
       </c>
       <c r="C22" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D22" t="s">
         <v>28</v>
@@ -1112,13 +1648,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="B23" t="s">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>113</v>
       </c>
       <c r="D23" t="s">
         <v>28</v>
@@ -1126,13 +1662,13 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B24" t="s">
         <v>28</v>
       </c>
       <c r="C24" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="D24" t="s">
         <v>28</v>
@@ -1140,13 +1676,13 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" t="s">
         <v>21</v>
-      </c>
-      <c r="C25" t="s">
-        <v>38</v>
       </c>
       <c r="D25" t="s">
         <v>28</v>
@@ -1154,13 +1690,13 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B26" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="C26" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="D26" t="s">
         <v>28</v>
@@ -1168,13 +1704,13 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B27" t="s">
-        <v>19</v>
+        <v>110</v>
       </c>
       <c r="C27" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D27" t="s">
         <v>28</v>
@@ -1182,13 +1718,13 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>66</v>
-      </c>
-      <c r="B28">
-        <v>1</v>
+        <v>61</v>
+      </c>
+      <c r="B28" t="s">
+        <v>27</v>
       </c>
       <c r="C28" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D28" t="s">
         <v>28</v>
@@ -1196,13 +1732,13 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>66</v>
-      </c>
-      <c r="B29">
-        <v>2</v>
+        <v>62</v>
+      </c>
+      <c r="B29" t="s">
+        <v>28</v>
       </c>
       <c r="C29" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="D29" t="s">
         <v>28</v>
@@ -1210,13 +1746,13 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B30" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C30" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="D30" t="s">
         <v>28</v>
@@ -1224,13 +1760,13 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="B31" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C31" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D31" t="s">
         <v>28</v>
@@ -1238,13 +1774,13 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B32" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C32" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D32" t="s">
         <v>28</v>
@@ -1252,13 +1788,13 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>69</v>
-      </c>
-      <c r="B33" t="s">
-        <v>8</v>
+        <v>66</v>
+      </c>
+      <c r="B33">
+        <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="D33" t="s">
         <v>28</v>
@@ -1266,13 +1802,13 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>69</v>
-      </c>
-      <c r="B34" t="s">
-        <v>9</v>
+        <v>66</v>
+      </c>
+      <c r="B34">
+        <v>2</v>
       </c>
       <c r="C34" t="s">
-        <v>9</v>
+        <v>67</v>
       </c>
       <c r="D34" t="s">
         <v>28</v>
@@ -1280,13 +1816,13 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B35" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C35" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D35" t="s">
         <v>28</v>
@@ -1294,13 +1830,13 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="B36" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="C36" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D36" t="s">
         <v>28</v>
@@ -1311,10 +1847,10 @@
         <v>69</v>
       </c>
       <c r="B37" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="C37" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D37" t="s">
         <v>28</v>
@@ -1325,10 +1861,10 @@
         <v>69</v>
       </c>
       <c r="B38" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C38" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D38" t="s">
         <v>28</v>
@@ -1336,13 +1872,13 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B39" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C39" t="s">
-        <v>65</v>
+        <v>9</v>
       </c>
       <c r="D39" t="s">
         <v>28</v>
@@ -1350,13 +1886,13 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="B40" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="C40" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="D40" t="s">
         <v>28</v>
@@ -1364,13 +1900,13 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B41" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="C41" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="D41" t="s">
         <v>28</v>
@@ -1378,20 +1914,90 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
+        <v>69</v>
+      </c>
+      <c r="B42" t="s">
+        <v>34</v>
+      </c>
+      <c r="C42" t="s">
+        <v>12</v>
+      </c>
+      <c r="D42" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>69</v>
+      </c>
+      <c r="B43" t="s">
+        <v>12</v>
+      </c>
+      <c r="C43" t="s">
+        <v>12</v>
+      </c>
+      <c r="D43" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>70</v>
+      </c>
+      <c r="B44" t="s">
+        <v>19</v>
+      </c>
+      <c r="C44" t="s">
+        <v>65</v>
+      </c>
+      <c r="D44" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>20</v>
+      </c>
+      <c r="B45" t="s">
+        <v>28</v>
+      </c>
+      <c r="C45" t="s">
+        <v>71</v>
+      </c>
+      <c r="D45" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>72</v>
+      </c>
+      <c r="B46" t="s">
+        <v>28</v>
+      </c>
+      <c r="C46" t="s">
+        <v>73</v>
+      </c>
+      <c r="D46" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
         <v>74</v>
       </c>
-      <c r="B42" t="s">
-        <v>28</v>
-      </c>
-      <c r="C42" t="s">
+      <c r="B47" t="s">
+        <v>28</v>
+      </c>
+      <c r="C47" t="s">
         <v>26</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D47" t="s">
         <v>28</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="5">
+  <dataValidations disablePrompts="1" count="5">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C6" xr:uid="{2FF3CD41-B9AC-419D-B52C-22CA2070CF17}">
       <formula1>hid4den</formula1>
     </dataValidation>
@@ -1404,7 +2010,7 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C3" xr:uid="{2A5C54BC-61FC-4225-9E96-2E3649904192}">
       <formula1>hid1den</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C28:C29" xr:uid="{A18C410F-13A8-4B2D-9CEE-4966E6792472}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C33:C34" xr:uid="{A18C410F-13A8-4B2D-9CEE-4966E6792472}">
       <formula1>hid29den</formula1>
     </dataValidation>
   </dataValidations>
@@ -1414,7 +2020,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5E74C28-9494-4104-81C6-5A34A8ECDBE0}">
-  <dimension ref="A1:D65"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.453125" bestFit="1" customWidth="1"/>
@@ -1855,13 +2461,13 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B32" t="s">
-        <v>27</v>
+        <v>110</v>
       </c>
       <c r="C32" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="D32" t="s">
         <v>28</v>
@@ -1872,7 +2478,7 @@
         <v>61</v>
       </c>
       <c r="B33" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C33" t="s">
         <v>27</v>
@@ -1886,10 +2492,10 @@
         <v>61</v>
       </c>
       <c r="B34" t="s">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="C34" t="s">
-        <v>99</v>
+        <v>27</v>
       </c>
       <c r="D34" t="s">
         <v>28</v>
@@ -1897,13 +2503,13 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B35" t="s">
-        <v>28</v>
+        <v>99</v>
       </c>
       <c r="C35" t="s">
-        <v>30</v>
+        <v>99</v>
       </c>
       <c r="D35" t="s">
         <v>28</v>
@@ -1911,13 +2517,13 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="B36" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C36" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D36" t="s">
         <v>28</v>
@@ -1928,10 +2534,10 @@
         <v>101</v>
       </c>
       <c r="B37" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C37" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D37" t="s">
         <v>28</v>
@@ -1939,13 +2545,13 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="B38" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C38" t="s">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="D38" t="s">
         <v>28</v>
@@ -1953,13 +2559,13 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>66</v>
-      </c>
-      <c r="B39">
-        <v>1</v>
+        <v>64</v>
+      </c>
+      <c r="B39" t="s">
+        <v>19</v>
       </c>
       <c r="C39" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="D39" t="s">
         <v>28</v>
@@ -1970,10 +2576,10 @@
         <v>66</v>
       </c>
       <c r="B40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="D40" t="s">
         <v>28</v>
@@ -1981,13 +2587,13 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>32</v>
-      </c>
-      <c r="B41" t="s">
-        <v>28</v>
+        <v>66</v>
+      </c>
+      <c r="B41">
+        <v>2</v>
       </c>
       <c r="C41" t="s">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="D41" t="s">
         <v>28</v>
@@ -1995,13 +2601,13 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="B42" t="s">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="C42" t="s">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="D42" t="s">
         <v>28</v>
@@ -2012,10 +2618,10 @@
         <v>69</v>
       </c>
       <c r="B43" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C43" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D43" t="s">
         <v>28</v>
@@ -2026,10 +2632,10 @@
         <v>69</v>
       </c>
       <c r="B44" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C44" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D44" t="s">
         <v>28</v>
@@ -2040,10 +2646,10 @@
         <v>69</v>
       </c>
       <c r="B45" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C45" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D45" t="s">
         <v>28</v>
@@ -2054,10 +2660,10 @@
         <v>69</v>
       </c>
       <c r="B46" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C46" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D46" t="s">
         <v>28</v>
@@ -2068,10 +2674,10 @@
         <v>69</v>
       </c>
       <c r="B47" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C47" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D47" t="s">
         <v>28</v>
@@ -2082,10 +2688,10 @@
         <v>69</v>
       </c>
       <c r="B48" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C48" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D48" t="s">
         <v>28</v>
@@ -2096,10 +2702,10 @@
         <v>69</v>
       </c>
       <c r="B49" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C49" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D49" t="s">
         <v>28</v>
@@ -2110,10 +2716,10 @@
         <v>69</v>
       </c>
       <c r="B50" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C50" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D50" t="s">
         <v>28</v>
@@ -2124,10 +2730,10 @@
         <v>69</v>
       </c>
       <c r="B51" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C51" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D51" t="s">
         <v>28</v>
@@ -2138,10 +2744,10 @@
         <v>69</v>
       </c>
       <c r="B52" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C52" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="D52" t="s">
         <v>28</v>
@@ -2152,10 +2758,10 @@
         <v>69</v>
       </c>
       <c r="B53" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C53" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D53" t="s">
         <v>28</v>
@@ -2166,10 +2772,10 @@
         <v>69</v>
       </c>
       <c r="B54" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C54" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D54" t="s">
         <v>28</v>
@@ -2180,10 +2786,10 @@
         <v>69</v>
       </c>
       <c r="B55" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C55" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D55" t="s">
         <v>28</v>
@@ -2194,10 +2800,10 @@
         <v>69</v>
       </c>
       <c r="B56" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C56" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D56" t="s">
         <v>28</v>
@@ -2208,10 +2814,10 @@
         <v>69</v>
       </c>
       <c r="B57" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C57" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D57" t="s">
         <v>28</v>
@@ -2222,10 +2828,10 @@
         <v>69</v>
       </c>
       <c r="B58" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C58" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D58" t="s">
         <v>28</v>
@@ -2236,10 +2842,10 @@
         <v>69</v>
       </c>
       <c r="B59" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C59" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D59" t="s">
         <v>28</v>
@@ -2247,13 +2853,13 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B60" t="s">
-        <v>19</v>
+        <v>109</v>
       </c>
       <c r="C60" t="s">
-        <v>65</v>
+        <v>109</v>
       </c>
       <c r="D60" t="s">
         <v>28</v>
@@ -2261,13 +2867,13 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="B61" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C61" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D61" t="s">
         <v>28</v>
@@ -2275,13 +2881,13 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="B62" t="s">
         <v>28</v>
       </c>
       <c r="C62" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D62" t="s">
         <v>28</v>
@@ -2289,13 +2895,13 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B63" t="s">
         <v>28</v>
       </c>
       <c r="C63" t="s">
-        <v>26</v>
+        <v>73</v>
       </c>
       <c r="D63" t="s">
         <v>28</v>
@@ -2303,13 +2909,13 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="B64" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="C64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D64" t="s">
         <v>28</v>
@@ -2320,12 +2926,26 @@
         <v>98</v>
       </c>
       <c r="B65" t="s">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="C65" t="s">
         <v>25</v>
       </c>
       <c r="D65" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>98</v>
+      </c>
+      <c r="B66" t="s">
+        <v>100</v>
+      </c>
+      <c r="C66" t="s">
+        <v>25</v>
+      </c>
+      <c r="D66" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2337,7 +2957,7 @@
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="6">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C39:C40" xr:uid="{806DEB49-2B61-4F7C-A4BD-A04E690DF9AD}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C40:C41" xr:uid="{806DEB49-2B61-4F7C-A4BD-A04E690DF9AD}">
       <formula1>hid29den</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C3" xr:uid="{014D6161-32C2-4B77-B51A-637FAA6094C0}">
@@ -2358,4 +2978,1832 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA2DBEE3-8864-4F5B-96E7-2590521BA3EC}">
+  <dimension ref="A1:D62"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B6" t="s">
+        <v>114</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C7">
+        <v>25</v>
+      </c>
+      <c r="D7" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>118</v>
+      </c>
+      <c r="B8" t="s">
+        <v>114</v>
+      </c>
+      <c r="C8">
+        <v>20</v>
+      </c>
+      <c r="D8" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>119</v>
+      </c>
+      <c r="B9" t="s">
+        <v>114</v>
+      </c>
+      <c r="C9" t="s">
+        <v>120</v>
+      </c>
+      <c r="D9" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>121</v>
+      </c>
+      <c r="B10" t="s">
+        <v>114</v>
+      </c>
+      <c r="C10">
+        <v>300</v>
+      </c>
+      <c r="D10" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B11" t="s">
+        <v>114</v>
+      </c>
+      <c r="C11" t="s">
+        <v>123</v>
+      </c>
+      <c r="D11" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>124</v>
+      </c>
+      <c r="B12" t="s">
+        <v>114</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>125</v>
+      </c>
+      <c r="B13" t="s">
+        <v>114</v>
+      </c>
+      <c r="C13">
+        <v>25</v>
+      </c>
+      <c r="D13" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>126</v>
+      </c>
+      <c r="B14" t="s">
+        <v>114</v>
+      </c>
+      <c r="C14">
+        <v>20</v>
+      </c>
+      <c r="D14" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>127</v>
+      </c>
+      <c r="B15" t="s">
+        <v>114</v>
+      </c>
+      <c r="C15" t="s">
+        <v>120</v>
+      </c>
+      <c r="D15" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>128</v>
+      </c>
+      <c r="B16" t="s">
+        <v>114</v>
+      </c>
+      <c r="C16">
+        <v>300</v>
+      </c>
+      <c r="D16" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>129</v>
+      </c>
+      <c r="B17" t="s">
+        <v>114</v>
+      </c>
+      <c r="C17" t="s">
+        <v>123</v>
+      </c>
+      <c r="D17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>130</v>
+      </c>
+      <c r="B18" t="s">
+        <v>114</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" t="s">
+        <v>114</v>
+      </c>
+      <c r="C19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" t="s">
+        <v>114</v>
+      </c>
+      <c r="C20" t="s">
+        <v>131</v>
+      </c>
+      <c r="D20" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>132</v>
+      </c>
+      <c r="B21" t="s">
+        <v>114</v>
+      </c>
+      <c r="C21" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>133</v>
+      </c>
+      <c r="B22" t="s">
+        <v>114</v>
+      </c>
+      <c r="C22" t="s">
+        <v>134</v>
+      </c>
+      <c r="D22" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>135</v>
+      </c>
+      <c r="B23" t="s">
+        <v>114</v>
+      </c>
+      <c r="C23" t="s">
+        <v>136</v>
+      </c>
+      <c r="D23" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>137</v>
+      </c>
+      <c r="B24" t="s">
+        <v>114</v>
+      </c>
+      <c r="C24" t="s">
+        <v>65</v>
+      </c>
+      <c r="D24" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>62</v>
+      </c>
+      <c r="B25" t="s">
+        <v>114</v>
+      </c>
+      <c r="C25" t="s">
+        <v>138</v>
+      </c>
+      <c r="D25" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" t="s">
+        <v>114</v>
+      </c>
+      <c r="C26" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" t="s">
+        <v>82</v>
+      </c>
+      <c r="C27" t="s">
+        <v>82</v>
+      </c>
+      <c r="D27" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B28" t="s">
+        <v>139</v>
+      </c>
+      <c r="C28" t="s">
+        <v>139</v>
+      </c>
+      <c r="D28" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29" t="s">
+        <v>4</v>
+      </c>
+      <c r="C29" t="s">
+        <v>4</v>
+      </c>
+      <c r="D29" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B30" t="s">
+        <v>83</v>
+      </c>
+      <c r="C30" t="s">
+        <v>83</v>
+      </c>
+      <c r="D30" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" t="s">
+        <v>140</v>
+      </c>
+      <c r="C31" t="s">
+        <v>140</v>
+      </c>
+      <c r="D31" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B32" t="s">
+        <v>0</v>
+      </c>
+      <c r="C32" t="s">
+        <v>0</v>
+      </c>
+      <c r="D32" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B33" t="s">
+        <v>141</v>
+      </c>
+      <c r="C33" t="s">
+        <v>142</v>
+      </c>
+      <c r="D33" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B34" t="s">
+        <v>143</v>
+      </c>
+      <c r="C34" t="s">
+        <v>143</v>
+      </c>
+      <c r="D34" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B35" t="s">
+        <v>144</v>
+      </c>
+      <c r="C35" t="s">
+        <v>144</v>
+      </c>
+      <c r="D35" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B36" t="s">
+        <v>145</v>
+      </c>
+      <c r="C36" t="s">
+        <v>145</v>
+      </c>
+      <c r="D36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B37" t="s">
+        <v>146</v>
+      </c>
+      <c r="C37" t="s">
+        <v>146</v>
+      </c>
+      <c r="D37" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B38" t="s">
+        <v>148</v>
+      </c>
+      <c r="C38" t="s">
+        <v>149</v>
+      </c>
+      <c r="D38" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B39" t="s">
+        <v>150</v>
+      </c>
+      <c r="C39" t="s">
+        <v>151</v>
+      </c>
+      <c r="D39" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B40" t="s">
+        <v>152</v>
+      </c>
+      <c r="C40" t="s">
+        <v>153</v>
+      </c>
+      <c r="D40" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B41" t="s">
+        <v>155</v>
+      </c>
+      <c r="C41" t="s">
+        <v>156</v>
+      </c>
+      <c r="D41" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B42" t="s">
+        <v>152</v>
+      </c>
+      <c r="C42" t="s">
+        <v>157</v>
+      </c>
+      <c r="D42" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B43" t="s">
+        <v>150</v>
+      </c>
+      <c r="C43" t="s">
+        <v>157</v>
+      </c>
+      <c r="D43" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B44" t="s">
+        <v>159</v>
+      </c>
+      <c r="C44" t="s">
+        <v>160</v>
+      </c>
+      <c r="D44" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B45" t="s">
+        <v>161</v>
+      </c>
+      <c r="C45" t="s">
+        <v>162</v>
+      </c>
+      <c r="D45" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B46" t="s">
+        <v>163</v>
+      </c>
+      <c r="C46" t="s">
+        <v>164</v>
+      </c>
+      <c r="D46" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B47" t="s">
+        <v>165</v>
+      </c>
+      <c r="C47" t="s">
+        <v>165</v>
+      </c>
+      <c r="D47" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B48" t="s">
+        <v>166</v>
+      </c>
+      <c r="C48" t="s">
+        <v>166</v>
+      </c>
+      <c r="D48" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B49" t="s">
+        <v>167</v>
+      </c>
+      <c r="C49" t="s">
+        <v>167</v>
+      </c>
+      <c r="D49" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B50" t="s">
+        <v>168</v>
+      </c>
+      <c r="C50" t="s">
+        <v>168</v>
+      </c>
+      <c r="D50" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B51" t="s">
+        <v>169</v>
+      </c>
+      <c r="C51" t="s">
+        <v>169</v>
+      </c>
+      <c r="D51" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B52" t="s">
+        <v>170</v>
+      </c>
+      <c r="C52" t="s">
+        <v>170</v>
+      </c>
+      <c r="D52" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B53" t="s">
+        <v>171</v>
+      </c>
+      <c r="C53" t="s">
+        <v>171</v>
+      </c>
+      <c r="D53" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B54" t="s">
+        <v>172</v>
+      </c>
+      <c r="C54" t="s">
+        <v>172</v>
+      </c>
+      <c r="D54" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B55" t="s">
+        <v>173</v>
+      </c>
+      <c r="C55" t="s">
+        <v>173</v>
+      </c>
+      <c r="D55" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B56" t="s">
+        <v>174</v>
+      </c>
+      <c r="C56" t="s">
+        <v>174</v>
+      </c>
+      <c r="D56" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B57" t="s">
+        <v>175</v>
+      </c>
+      <c r="C57" t="s">
+        <v>175</v>
+      </c>
+      <c r="D57" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B58" t="s">
+        <v>176</v>
+      </c>
+      <c r="C58" t="s">
+        <v>176</v>
+      </c>
+      <c r="D58" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B59" t="s">
+        <v>177</v>
+      </c>
+      <c r="C59" t="s">
+        <v>177</v>
+      </c>
+      <c r="D59" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B60" t="s">
+        <v>178</v>
+      </c>
+      <c r="C60" t="s">
+        <v>178</v>
+      </c>
+      <c r="D60" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B61" t="s">
+        <v>179</v>
+      </c>
+      <c r="C61" t="s">
+        <v>179</v>
+      </c>
+      <c r="D61" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B62" t="s">
+        <v>180</v>
+      </c>
+      <c r="C62" t="s">
+        <v>180</v>
+      </c>
+      <c r="D62" t="s">
+        <v>114</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C38:C40" xr:uid="{04D217AF-B832-4B10-9999-85CE3DA0C6D4}">
+      <formula1>hid46den</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAB77534-D539-4D66-91F8-F015AB63AC99}">
+  <dimension ref="A1:D66"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" t="s">
+        <v>181</v>
+      </c>
+      <c r="C5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B6" t="s">
+        <v>181</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B7" t="s">
+        <v>181</v>
+      </c>
+      <c r="C7">
+        <v>25</v>
+      </c>
+      <c r="D7" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B8" t="s">
+        <v>181</v>
+      </c>
+      <c r="C8">
+        <v>20</v>
+      </c>
+      <c r="D8" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B9" t="s">
+        <v>181</v>
+      </c>
+      <c r="C9" t="s">
+        <v>120</v>
+      </c>
+      <c r="D9" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B10" t="s">
+        <v>181</v>
+      </c>
+      <c r="C10">
+        <v>300</v>
+      </c>
+      <c r="D10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B11" t="s">
+        <v>181</v>
+      </c>
+      <c r="C11" t="s">
+        <v>123</v>
+      </c>
+      <c r="D11" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B12" t="s">
+        <v>181</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B13" t="s">
+        <v>181</v>
+      </c>
+      <c r="C13">
+        <v>25</v>
+      </c>
+      <c r="D13" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B14" t="s">
+        <v>181</v>
+      </c>
+      <c r="C14">
+        <v>20</v>
+      </c>
+      <c r="D14" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B15" t="s">
+        <v>181</v>
+      </c>
+      <c r="C15" t="s">
+        <v>120</v>
+      </c>
+      <c r="D15" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B16" t="s">
+        <v>181</v>
+      </c>
+      <c r="C16">
+        <v>300</v>
+      </c>
+      <c r="D16" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B17" t="s">
+        <v>181</v>
+      </c>
+      <c r="C17" t="s">
+        <v>123</v>
+      </c>
+      <c r="D17" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B18" t="s">
+        <v>181</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" t="s">
+        <v>181</v>
+      </c>
+      <c r="C19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" t="s">
+        <v>181</v>
+      </c>
+      <c r="C20" t="s">
+        <v>131</v>
+      </c>
+      <c r="D20" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B21" t="s">
+        <v>181</v>
+      </c>
+      <c r="C21" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B22" t="s">
+        <v>181</v>
+      </c>
+      <c r="C22" t="s">
+        <v>134</v>
+      </c>
+      <c r="D22" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B23" t="s">
+        <v>181</v>
+      </c>
+      <c r="C23" t="s">
+        <v>136</v>
+      </c>
+      <c r="D23" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B24" t="s">
+        <v>181</v>
+      </c>
+      <c r="C24" t="s">
+        <v>138</v>
+      </c>
+      <c r="D24" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B25" t="s">
+        <v>181</v>
+      </c>
+      <c r="C25" t="s">
+        <v>65</v>
+      </c>
+      <c r="D25" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B26" t="s">
+        <v>181</v>
+      </c>
+      <c r="C26" t="s">
+        <v>183</v>
+      </c>
+      <c r="D26" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B27" t="s">
+        <v>181</v>
+      </c>
+      <c r="C27" t="s">
+        <v>57</v>
+      </c>
+      <c r="D27" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B28" t="s">
+        <v>82</v>
+      </c>
+      <c r="C28" t="s">
+        <v>82</v>
+      </c>
+      <c r="D28" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29" t="s">
+        <v>139</v>
+      </c>
+      <c r="C29" t="s">
+        <v>139</v>
+      </c>
+      <c r="D29" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B30" t="s">
+        <v>4</v>
+      </c>
+      <c r="C30" t="s">
+        <v>4</v>
+      </c>
+      <c r="D30" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" t="s">
+        <v>83</v>
+      </c>
+      <c r="C31" t="s">
+        <v>83</v>
+      </c>
+      <c r="D31" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B32" t="s">
+        <v>140</v>
+      </c>
+      <c r="C32" t="s">
+        <v>140</v>
+      </c>
+      <c r="D32" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B33" t="s">
+        <v>0</v>
+      </c>
+      <c r="C33" t="s">
+        <v>0</v>
+      </c>
+      <c r="D33" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B34" t="s">
+        <v>141</v>
+      </c>
+      <c r="C34" t="s">
+        <v>142</v>
+      </c>
+      <c r="D34" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B35" t="s">
+        <v>143</v>
+      </c>
+      <c r="C35" t="s">
+        <v>143</v>
+      </c>
+      <c r="D35" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B36" t="s">
+        <v>144</v>
+      </c>
+      <c r="C36" t="s">
+        <v>144</v>
+      </c>
+      <c r="D36" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B37" t="s">
+        <v>145</v>
+      </c>
+      <c r="C37" t="s">
+        <v>145</v>
+      </c>
+      <c r="D37" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B38" t="s">
+        <v>146</v>
+      </c>
+      <c r="C38" t="s">
+        <v>146</v>
+      </c>
+      <c r="D38" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B39" t="s">
+        <v>148</v>
+      </c>
+      <c r="C39" t="s">
+        <v>149</v>
+      </c>
+      <c r="D39" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B40" t="s">
+        <v>150</v>
+      </c>
+      <c r="C40" t="s">
+        <v>151</v>
+      </c>
+      <c r="D40" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B41" t="s">
+        <v>152</v>
+      </c>
+      <c r="C41" t="s">
+        <v>153</v>
+      </c>
+      <c r="D41" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B42" t="s">
+        <v>155</v>
+      </c>
+      <c r="C42" t="s">
+        <v>156</v>
+      </c>
+      <c r="D42" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B43" t="s">
+        <v>152</v>
+      </c>
+      <c r="C43" t="s">
+        <v>157</v>
+      </c>
+      <c r="D43" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B44" t="s">
+        <v>150</v>
+      </c>
+      <c r="C44" t="s">
+        <v>157</v>
+      </c>
+      <c r="D44" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B45" t="s">
+        <v>159</v>
+      </c>
+      <c r="C45" t="s">
+        <v>160</v>
+      </c>
+      <c r="D45" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B46" t="s">
+        <v>161</v>
+      </c>
+      <c r="C46" t="s">
+        <v>162</v>
+      </c>
+      <c r="D46" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B47" t="s">
+        <v>163</v>
+      </c>
+      <c r="C47" t="s">
+        <v>164</v>
+      </c>
+      <c r="D47" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B48" t="s">
+        <v>159</v>
+      </c>
+      <c r="C48" t="s">
+        <v>184</v>
+      </c>
+      <c r="D48" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B49" t="s">
+        <v>161</v>
+      </c>
+      <c r="C49" t="s">
+        <v>184</v>
+      </c>
+      <c r="D49" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B50" t="s">
+        <v>163</v>
+      </c>
+      <c r="C50" t="s">
+        <v>184</v>
+      </c>
+      <c r="D50" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B51" t="s">
+        <v>165</v>
+      </c>
+      <c r="C51" t="s">
+        <v>165</v>
+      </c>
+      <c r="D51" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B52" t="s">
+        <v>166</v>
+      </c>
+      <c r="C52" t="s">
+        <v>166</v>
+      </c>
+      <c r="D52" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B53" t="s">
+        <v>167</v>
+      </c>
+      <c r="C53" t="s">
+        <v>167</v>
+      </c>
+      <c r="D53" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B54" t="s">
+        <v>168</v>
+      </c>
+      <c r="C54" t="s">
+        <v>168</v>
+      </c>
+      <c r="D54" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B55" t="s">
+        <v>169</v>
+      </c>
+      <c r="C55" t="s">
+        <v>169</v>
+      </c>
+      <c r="D55" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B56" t="s">
+        <v>170</v>
+      </c>
+      <c r="C56" t="s">
+        <v>170</v>
+      </c>
+      <c r="D56" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B57" t="s">
+        <v>171</v>
+      </c>
+      <c r="C57" t="s">
+        <v>171</v>
+      </c>
+      <c r="D57" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B58" t="s">
+        <v>172</v>
+      </c>
+      <c r="C58" t="s">
+        <v>172</v>
+      </c>
+      <c r="D58" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B59" t="s">
+        <v>173</v>
+      </c>
+      <c r="C59" t="s">
+        <v>173</v>
+      </c>
+      <c r="D59" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B60" t="s">
+        <v>174</v>
+      </c>
+      <c r="C60" t="s">
+        <v>174</v>
+      </c>
+      <c r="D60" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B61" t="s">
+        <v>175</v>
+      </c>
+      <c r="C61" t="s">
+        <v>175</v>
+      </c>
+      <c r="D61" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B62" t="s">
+        <v>176</v>
+      </c>
+      <c r="C62" t="s">
+        <v>176</v>
+      </c>
+      <c r="D62" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A63" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B63" t="s">
+        <v>177</v>
+      </c>
+      <c r="C63" t="s">
+        <v>177</v>
+      </c>
+      <c r="D63" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A64" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B64" t="s">
+        <v>178</v>
+      </c>
+      <c r="C64" t="s">
+        <v>178</v>
+      </c>
+      <c r="D64" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A65" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B65" t="s">
+        <v>179</v>
+      </c>
+      <c r="C65" t="s">
+        <v>179</v>
+      </c>
+      <c r="D65" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A66" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B66" t="s">
+        <v>180</v>
+      </c>
+      <c r="C66" t="s">
+        <v>180</v>
+      </c>
+      <c r="D66" t="s">
+        <v>181</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C48:C50" xr:uid="{73D45787-6686-4AE9-89C4-12DD6369A6DC}">
+      <formula1>hid25den</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C42:C44" xr:uid="{AEE306AE-A90F-4EED-B643-69C32D1BDA3D}">
+      <formula1>hid17den</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C39:C41" xr:uid="{F77E7CFC-6F03-46E5-8C3C-3752D95F427A}">
+      <formula1>hid16den</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/config/Ajio_dropdown.xlsx
+++ b/config/Ajio_dropdown.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\our data\KPA\NEW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C90A248-8AB4-46EE-89B9-DA07E46C0D7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E3FFDC3-DB58-4CC7-8289-609FE8563963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="748" activeTab="3" xr2:uid="{C0D2C78A-6BFE-401C-9027-E5C9268B4C7B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="748" activeTab="2" xr2:uid="{C0D2C78A-6BFE-401C-9027-E5C9268B4C7B}"/>
   </bookViews>
   <sheets>
     <sheet name="Dropdown-Tshirts" sheetId="5" r:id="rId1"/>
@@ -736,9 +736,6 @@
       <sheetData sheetId="1"/>
       <sheetData sheetId="2">
         <row r="1">
-          <cell r="F1" t="str">
-            <v>CM</v>
-          </cell>
           <cell r="Q1" t="str">
             <v>Canvas upper</v>
           </cell>
@@ -2984,6 +2981,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA2DBEE3-8864-4F5B-96E7-2590521BA3EC}">
   <dimension ref="A1:D62"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="30.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.54296875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -3867,6 +3868,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAB77534-D539-4D66-91F8-F015AB63AC99}">
   <dimension ref="A1:D66"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="30.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.54296875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">

--- a/config/Ajio_dropdown.xlsx
+++ b/config/Ajio_dropdown.xlsx
@@ -8,20 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\our data\KPA\NEW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E3FFDC3-DB58-4CC7-8289-609FE8563963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38B2AAEB-E220-4E9C-ADC6-34031645FB96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="748" activeTab="2" xr2:uid="{C0D2C78A-6BFE-401C-9027-E5C9268B4C7B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="748" firstSheet="2" activeTab="5" xr2:uid="{C0D2C78A-6BFE-401C-9027-E5C9268B4C7B}"/>
   </bookViews>
   <sheets>
     <sheet name="Dropdown-Tshirts" sheetId="5" r:id="rId1"/>
     <sheet name="Dropdown-Kids Tshirts" sheetId="6" r:id="rId2"/>
     <sheet name="Dropdown-Boys Sandal" sheetId="7" r:id="rId3"/>
     <sheet name="Dropdown-Boys Shoes" sheetId="8" r:id="rId4"/>
+    <sheet name="Dropdown-Girls Shoes" sheetId="9" r:id="rId5"/>
+    <sheet name="Dropdown-Girls Sandal" sheetId="10" r:id="rId6"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId5"/>
+    <externalReference r:id="rId7"/>
   </externalReferences>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dropdown-Boys Sandal'!$A$1:$D$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Dropdown-Boys Shoes'!$A$1:$D$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Dropdown-Girls Sandal'!$A$1:$D$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Dropdown-Girls Shoes'!$A$1:$D$63</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dropdown-Kids Tshirts'!$A$1:$D$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dropdown-Tshirts'!$A$1:$D$1</definedName>
     <definedName name="hid16den">[1]sheetForStoringExtraValues!$Q$1:$Q$25</definedName>
@@ -56,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1410" uniqueCount="193">
   <si>
     <t>Blue</t>
   </si>
@@ -611,6 +617,30 @@
   </si>
   <si>
     <t>Slip-ons</t>
+  </si>
+  <si>
+    <t>Flat</t>
+  </si>
+  <si>
+    <t>Sandals</t>
+  </si>
+  <si>
+    <t>Girls Shoes</t>
+  </si>
+  <si>
+    <t>EVA sole</t>
+  </si>
+  <si>
+    <t>Slip-on</t>
+  </si>
+  <si>
+    <t>Flat shoes</t>
+  </si>
+  <si>
+    <t>Slip-Ons</t>
+  </si>
+  <si>
+    <t>Girls Sandal</t>
   </si>
 </sst>
 </file>
@@ -3302,7 +3332,7 @@
         <v>114</v>
       </c>
       <c r="C23" t="s">
-        <v>136</v>
+        <v>185</v>
       </c>
       <c r="D23" t="s">
         <v>114</v>
@@ -3330,7 +3360,7 @@
         <v>114</v>
       </c>
       <c r="C25" t="s">
-        <v>138</v>
+        <v>186</v>
       </c>
       <c r="D25" t="s">
         <v>114</v>
@@ -4811,4 +4841,1755 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60BD06E8-0BFD-45FE-B2FE-9F43CC89C4A6}">
+  <dimension ref="A1:D63"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="30.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D3" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" t="s">
+        <v>187</v>
+      </c>
+      <c r="C5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B6" t="s">
+        <v>187</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C7">
+        <v>25</v>
+      </c>
+      <c r="D7" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>118</v>
+      </c>
+      <c r="B8" t="s">
+        <v>187</v>
+      </c>
+      <c r="C8">
+        <v>20</v>
+      </c>
+      <c r="D8" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>119</v>
+      </c>
+      <c r="B9" t="s">
+        <v>187</v>
+      </c>
+      <c r="C9" t="s">
+        <v>120</v>
+      </c>
+      <c r="D9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>121</v>
+      </c>
+      <c r="B10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C10">
+        <v>300</v>
+      </c>
+      <c r="D10" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B11" t="s">
+        <v>187</v>
+      </c>
+      <c r="C11" t="s">
+        <v>123</v>
+      </c>
+      <c r="D11" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>124</v>
+      </c>
+      <c r="B12" t="s">
+        <v>187</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>125</v>
+      </c>
+      <c r="B13" t="s">
+        <v>187</v>
+      </c>
+      <c r="C13">
+        <v>25</v>
+      </c>
+      <c r="D13" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>126</v>
+      </c>
+      <c r="B14" t="s">
+        <v>187</v>
+      </c>
+      <c r="C14">
+        <v>20</v>
+      </c>
+      <c r="D14" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>127</v>
+      </c>
+      <c r="B15" t="s">
+        <v>187</v>
+      </c>
+      <c r="C15" t="s">
+        <v>120</v>
+      </c>
+      <c r="D15" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>128</v>
+      </c>
+      <c r="B16" t="s">
+        <v>187</v>
+      </c>
+      <c r="C16">
+        <v>300</v>
+      </c>
+      <c r="D16" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>129</v>
+      </c>
+      <c r="B17" t="s">
+        <v>187</v>
+      </c>
+      <c r="C17" t="s">
+        <v>123</v>
+      </c>
+      <c r="D17" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>130</v>
+      </c>
+      <c r="B18" t="s">
+        <v>187</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" t="s">
+        <v>187</v>
+      </c>
+      <c r="C19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" t="s">
+        <v>187</v>
+      </c>
+      <c r="C20" t="s">
+        <v>131</v>
+      </c>
+      <c r="D20" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>133</v>
+      </c>
+      <c r="B21" t="s">
+        <v>187</v>
+      </c>
+      <c r="C21" t="s">
+        <v>134</v>
+      </c>
+      <c r="D21" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>135</v>
+      </c>
+      <c r="B22" t="s">
+        <v>187</v>
+      </c>
+      <c r="C22" t="s">
+        <v>136</v>
+      </c>
+      <c r="D22" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>62</v>
+      </c>
+      <c r="B23" t="s">
+        <v>187</v>
+      </c>
+      <c r="C23" t="s">
+        <v>191</v>
+      </c>
+      <c r="D23" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>56</v>
+      </c>
+      <c r="B24" t="s">
+        <v>187</v>
+      </c>
+      <c r="C24" t="s">
+        <v>57</v>
+      </c>
+      <c r="D24" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" t="s">
+        <v>82</v>
+      </c>
+      <c r="C25" t="s">
+        <v>82</v>
+      </c>
+      <c r="D25" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" t="s">
+        <v>139</v>
+      </c>
+      <c r="C26" t="s">
+        <v>139</v>
+      </c>
+      <c r="D26" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" t="s">
+        <v>4</v>
+      </c>
+      <c r="C27" t="s">
+        <v>4</v>
+      </c>
+      <c r="D27" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>52</v>
+      </c>
+      <c r="B28" t="s">
+        <v>83</v>
+      </c>
+      <c r="C28" t="s">
+        <v>83</v>
+      </c>
+      <c r="D28" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29" t="s">
+        <v>140</v>
+      </c>
+      <c r="C29" t="s">
+        <v>140</v>
+      </c>
+      <c r="D29" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>52</v>
+      </c>
+      <c r="B30" t="s">
+        <v>0</v>
+      </c>
+      <c r="C30" t="s">
+        <v>0</v>
+      </c>
+      <c r="D30" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" t="s">
+        <v>141</v>
+      </c>
+      <c r="C31" t="s">
+        <v>142</v>
+      </c>
+      <c r="D31" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>52</v>
+      </c>
+      <c r="B32" t="s">
+        <v>143</v>
+      </c>
+      <c r="C32" t="s">
+        <v>143</v>
+      </c>
+      <c r="D32" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>52</v>
+      </c>
+      <c r="B33" t="s">
+        <v>144</v>
+      </c>
+      <c r="C33" t="s">
+        <v>144</v>
+      </c>
+      <c r="D33" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>52</v>
+      </c>
+      <c r="B34" t="s">
+        <v>145</v>
+      </c>
+      <c r="C34" t="s">
+        <v>145</v>
+      </c>
+      <c r="D34" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>52</v>
+      </c>
+      <c r="B35" t="s">
+        <v>146</v>
+      </c>
+      <c r="C35" t="s">
+        <v>146</v>
+      </c>
+      <c r="D35" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>147</v>
+      </c>
+      <c r="B36" t="s">
+        <v>148</v>
+      </c>
+      <c r="C36" t="s">
+        <v>149</v>
+      </c>
+      <c r="D36" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>147</v>
+      </c>
+      <c r="B37" t="s">
+        <v>150</v>
+      </c>
+      <c r="C37" t="s">
+        <v>151</v>
+      </c>
+      <c r="D37" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>147</v>
+      </c>
+      <c r="B38" t="s">
+        <v>152</v>
+      </c>
+      <c r="C38" t="s">
+        <v>153</v>
+      </c>
+      <c r="D38" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>154</v>
+      </c>
+      <c r="B39" t="s">
+        <v>155</v>
+      </c>
+      <c r="C39" t="s">
+        <v>156</v>
+      </c>
+      <c r="D39" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>154</v>
+      </c>
+      <c r="B40" t="s">
+        <v>152</v>
+      </c>
+      <c r="C40" t="s">
+        <v>157</v>
+      </c>
+      <c r="D40" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>154</v>
+      </c>
+      <c r="B41" t="s">
+        <v>150</v>
+      </c>
+      <c r="C41" t="s">
+        <v>188</v>
+      </c>
+      <c r="D41" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>158</v>
+      </c>
+      <c r="B42" t="s">
+        <v>159</v>
+      </c>
+      <c r="C42" t="s">
+        <v>159</v>
+      </c>
+      <c r="D42" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>158</v>
+      </c>
+      <c r="B43" t="s">
+        <v>161</v>
+      </c>
+      <c r="C43" t="s">
+        <v>189</v>
+      </c>
+      <c r="D43" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>158</v>
+      </c>
+      <c r="B44" t="s">
+        <v>163</v>
+      </c>
+      <c r="C44" t="s">
+        <v>164</v>
+      </c>
+      <c r="D44" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>70</v>
+      </c>
+      <c r="B45" t="s">
+        <v>159</v>
+      </c>
+      <c r="C45" t="s">
+        <v>190</v>
+      </c>
+      <c r="D45" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>70</v>
+      </c>
+      <c r="B46" t="s">
+        <v>161</v>
+      </c>
+      <c r="C46" t="s">
+        <v>190</v>
+      </c>
+      <c r="D46" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>70</v>
+      </c>
+      <c r="B47" t="s">
+        <v>163</v>
+      </c>
+      <c r="C47" t="s">
+        <v>190</v>
+      </c>
+      <c r="D47" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>69</v>
+      </c>
+      <c r="B48" t="s">
+        <v>165</v>
+      </c>
+      <c r="C48" t="s">
+        <v>165</v>
+      </c>
+      <c r="D48" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>69</v>
+      </c>
+      <c r="B49" t="s">
+        <v>166</v>
+      </c>
+      <c r="C49" t="s">
+        <v>166</v>
+      </c>
+      <c r="D49" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>69</v>
+      </c>
+      <c r="B50" t="s">
+        <v>167</v>
+      </c>
+      <c r="C50" t="s">
+        <v>167</v>
+      </c>
+      <c r="D50" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>69</v>
+      </c>
+      <c r="B51" t="s">
+        <v>168</v>
+      </c>
+      <c r="C51" t="s">
+        <v>168</v>
+      </c>
+      <c r="D51" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>69</v>
+      </c>
+      <c r="B52" t="s">
+        <v>169</v>
+      </c>
+      <c r="C52" t="s">
+        <v>169</v>
+      </c>
+      <c r="D52" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>69</v>
+      </c>
+      <c r="B53" t="s">
+        <v>170</v>
+      </c>
+      <c r="C53" t="s">
+        <v>170</v>
+      </c>
+      <c r="D53" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>69</v>
+      </c>
+      <c r="B54" t="s">
+        <v>171</v>
+      </c>
+      <c r="C54" t="s">
+        <v>171</v>
+      </c>
+      <c r="D54" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>69</v>
+      </c>
+      <c r="B55" t="s">
+        <v>172</v>
+      </c>
+      <c r="C55" t="s">
+        <v>172</v>
+      </c>
+      <c r="D55" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>69</v>
+      </c>
+      <c r="B56" t="s">
+        <v>173</v>
+      </c>
+      <c r="C56" t="s">
+        <v>173</v>
+      </c>
+      <c r="D56" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>69</v>
+      </c>
+      <c r="B57" t="s">
+        <v>174</v>
+      </c>
+      <c r="C57" t="s">
+        <v>174</v>
+      </c>
+      <c r="D57" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>69</v>
+      </c>
+      <c r="B58" t="s">
+        <v>175</v>
+      </c>
+      <c r="C58" t="s">
+        <v>175</v>
+      </c>
+      <c r="D58" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>69</v>
+      </c>
+      <c r="B59" t="s">
+        <v>176</v>
+      </c>
+      <c r="C59" t="s">
+        <v>176</v>
+      </c>
+      <c r="D59" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>69</v>
+      </c>
+      <c r="B60" t="s">
+        <v>177</v>
+      </c>
+      <c r="C60" t="s">
+        <v>177</v>
+      </c>
+      <c r="D60" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>69</v>
+      </c>
+      <c r="B61" t="s">
+        <v>178</v>
+      </c>
+      <c r="C61" t="s">
+        <v>178</v>
+      </c>
+      <c r="D61" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>69</v>
+      </c>
+      <c r="B62" t="s">
+        <v>179</v>
+      </c>
+      <c r="C62" t="s">
+        <v>179</v>
+      </c>
+      <c r="D62" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>69</v>
+      </c>
+      <c r="B63" t="s">
+        <v>180</v>
+      </c>
+      <c r="C63" t="s">
+        <v>180</v>
+      </c>
+      <c r="D63" t="s">
+        <v>187</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8EAFBF2-082E-4517-8E83-1565B0410884}">
+  <dimension ref="A1:D60"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" t="s">
+        <v>192</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" t="s">
+        <v>192</v>
+      </c>
+      <c r="C5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B6" t="s">
+        <v>192</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B7" t="s">
+        <v>192</v>
+      </c>
+      <c r="C7">
+        <v>25</v>
+      </c>
+      <c r="D7" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>118</v>
+      </c>
+      <c r="B8" t="s">
+        <v>192</v>
+      </c>
+      <c r="C8">
+        <v>20</v>
+      </c>
+      <c r="D8" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>119</v>
+      </c>
+      <c r="B9" t="s">
+        <v>192</v>
+      </c>
+      <c r="C9" t="s">
+        <v>120</v>
+      </c>
+      <c r="D9" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>121</v>
+      </c>
+      <c r="B10" t="s">
+        <v>192</v>
+      </c>
+      <c r="C10">
+        <v>300</v>
+      </c>
+      <c r="D10" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B11" t="s">
+        <v>192</v>
+      </c>
+      <c r="C11" t="s">
+        <v>123</v>
+      </c>
+      <c r="D11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>124</v>
+      </c>
+      <c r="B12" t="s">
+        <v>192</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>125</v>
+      </c>
+      <c r="B13" t="s">
+        <v>192</v>
+      </c>
+      <c r="C13">
+        <v>25</v>
+      </c>
+      <c r="D13" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>126</v>
+      </c>
+      <c r="B14" t="s">
+        <v>192</v>
+      </c>
+      <c r="C14">
+        <v>20</v>
+      </c>
+      <c r="D14" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>127</v>
+      </c>
+      <c r="B15" t="s">
+        <v>192</v>
+      </c>
+      <c r="C15" t="s">
+        <v>120</v>
+      </c>
+      <c r="D15" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>128</v>
+      </c>
+      <c r="B16" t="s">
+        <v>192</v>
+      </c>
+      <c r="C16">
+        <v>300</v>
+      </c>
+      <c r="D16" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>129</v>
+      </c>
+      <c r="B17" t="s">
+        <v>192</v>
+      </c>
+      <c r="C17" t="s">
+        <v>123</v>
+      </c>
+      <c r="D17" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>130</v>
+      </c>
+      <c r="B18" t="s">
+        <v>192</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" t="s">
+        <v>192</v>
+      </c>
+      <c r="C19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" t="s">
+        <v>192</v>
+      </c>
+      <c r="C20" t="s">
+        <v>131</v>
+      </c>
+      <c r="D20" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>133</v>
+      </c>
+      <c r="B21" t="s">
+        <v>192</v>
+      </c>
+      <c r="C21" t="s">
+        <v>134</v>
+      </c>
+      <c r="D21" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>135</v>
+      </c>
+      <c r="B22" t="s">
+        <v>192</v>
+      </c>
+      <c r="C22" t="s">
+        <v>185</v>
+      </c>
+      <c r="D22" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>62</v>
+      </c>
+      <c r="B23" t="s">
+        <v>192</v>
+      </c>
+      <c r="C23" t="s">
+        <v>186</v>
+      </c>
+      <c r="D23" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>56</v>
+      </c>
+      <c r="B24" t="s">
+        <v>192</v>
+      </c>
+      <c r="C24" t="s">
+        <v>57</v>
+      </c>
+      <c r="D24" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" t="s">
+        <v>82</v>
+      </c>
+      <c r="C25" t="s">
+        <v>82</v>
+      </c>
+      <c r="D25" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" t="s">
+        <v>139</v>
+      </c>
+      <c r="C26" t="s">
+        <v>139</v>
+      </c>
+      <c r="D26" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" t="s">
+        <v>4</v>
+      </c>
+      <c r="C27" t="s">
+        <v>4</v>
+      </c>
+      <c r="D27" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B28" t="s">
+        <v>83</v>
+      </c>
+      <c r="C28" t="s">
+        <v>83</v>
+      </c>
+      <c r="D28" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29" t="s">
+        <v>140</v>
+      </c>
+      <c r="C29" t="s">
+        <v>140</v>
+      </c>
+      <c r="D29" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B30" t="s">
+        <v>0</v>
+      </c>
+      <c r="C30" t="s">
+        <v>0</v>
+      </c>
+      <c r="D30" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" t="s">
+        <v>141</v>
+      </c>
+      <c r="C31" t="s">
+        <v>142</v>
+      </c>
+      <c r="D31" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B32" t="s">
+        <v>143</v>
+      </c>
+      <c r="C32" t="s">
+        <v>143</v>
+      </c>
+      <c r="D32" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B33" t="s">
+        <v>144</v>
+      </c>
+      <c r="C33" t="s">
+        <v>144</v>
+      </c>
+      <c r="D33" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B34" t="s">
+        <v>145</v>
+      </c>
+      <c r="C34" t="s">
+        <v>145</v>
+      </c>
+      <c r="D34" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B35" t="s">
+        <v>146</v>
+      </c>
+      <c r="C35" t="s">
+        <v>146</v>
+      </c>
+      <c r="D35" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B36" t="s">
+        <v>148</v>
+      </c>
+      <c r="C36" t="s">
+        <v>149</v>
+      </c>
+      <c r="D36" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B37" t="s">
+        <v>150</v>
+      </c>
+      <c r="C37" t="s">
+        <v>151</v>
+      </c>
+      <c r="D37" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B38" t="s">
+        <v>152</v>
+      </c>
+      <c r="C38" t="s">
+        <v>153</v>
+      </c>
+      <c r="D38" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B39" t="s">
+        <v>155</v>
+      </c>
+      <c r="C39" t="s">
+        <v>156</v>
+      </c>
+      <c r="D39" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B40" t="s">
+        <v>152</v>
+      </c>
+      <c r="C40" t="s">
+        <v>157</v>
+      </c>
+      <c r="D40" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B41" t="s">
+        <v>150</v>
+      </c>
+      <c r="C41" t="s">
+        <v>157</v>
+      </c>
+      <c r="D41" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B42" t="s">
+        <v>159</v>
+      </c>
+      <c r="C42" t="s">
+        <v>160</v>
+      </c>
+      <c r="D42" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B43" t="s">
+        <v>161</v>
+      </c>
+      <c r="C43" t="s">
+        <v>162</v>
+      </c>
+      <c r="D43" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B44" t="s">
+        <v>163</v>
+      </c>
+      <c r="C44" t="s">
+        <v>164</v>
+      </c>
+      <c r="D44" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B45" t="s">
+        <v>165</v>
+      </c>
+      <c r="C45" t="s">
+        <v>165</v>
+      </c>
+      <c r="D45" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B46" t="s">
+        <v>166</v>
+      </c>
+      <c r="C46" t="s">
+        <v>166</v>
+      </c>
+      <c r="D46" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B47" t="s">
+        <v>167</v>
+      </c>
+      <c r="C47" t="s">
+        <v>167</v>
+      </c>
+      <c r="D47" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B48" t="s">
+        <v>168</v>
+      </c>
+      <c r="C48" t="s">
+        <v>168</v>
+      </c>
+      <c r="D48" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B49" t="s">
+        <v>169</v>
+      </c>
+      <c r="C49" t="s">
+        <v>169</v>
+      </c>
+      <c r="D49" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B50" t="s">
+        <v>170</v>
+      </c>
+      <c r="C50" t="s">
+        <v>170</v>
+      </c>
+      <c r="D50" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B51" t="s">
+        <v>171</v>
+      </c>
+      <c r="C51" t="s">
+        <v>171</v>
+      </c>
+      <c r="D51" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B52" t="s">
+        <v>172</v>
+      </c>
+      <c r="C52" t="s">
+        <v>172</v>
+      </c>
+      <c r="D52" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B53" t="s">
+        <v>173</v>
+      </c>
+      <c r="C53" t="s">
+        <v>173</v>
+      </c>
+      <c r="D53" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B54" t="s">
+        <v>174</v>
+      </c>
+      <c r="C54" t="s">
+        <v>174</v>
+      </c>
+      <c r="D54" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B55" t="s">
+        <v>175</v>
+      </c>
+      <c r="C55" t="s">
+        <v>175</v>
+      </c>
+      <c r="D55" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B56" t="s">
+        <v>176</v>
+      </c>
+      <c r="C56" t="s">
+        <v>176</v>
+      </c>
+      <c r="D56" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B57" t="s">
+        <v>177</v>
+      </c>
+      <c r="C57" t="s">
+        <v>177</v>
+      </c>
+      <c r="D57" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B58" t="s">
+        <v>178</v>
+      </c>
+      <c r="C58" t="s">
+        <v>178</v>
+      </c>
+      <c r="D58" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B59" t="s">
+        <v>179</v>
+      </c>
+      <c r="C59" t="s">
+        <v>179</v>
+      </c>
+      <c r="D59" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B60" t="s">
+        <v>180</v>
+      </c>
+      <c r="C60" t="s">
+        <v>180</v>
+      </c>
+      <c r="D60" t="s">
+        <v>192</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C36:C38" xr:uid="{95FFA84E-B893-460B-AD4F-782C11CBDBBD}">
+      <formula1>hid46den</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>